--- a/examples/mlx/model.xlsx
+++ b/examples/mlx/model.xlsx
@@ -27,7 +27,7 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Operating!$A$1:$I$36</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Readme!$A$1:$H$89</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Sensitivities!$A$1:$I$46</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$H$52</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$I$36</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Valuation!$A$1:$I$46</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -71,9 +71,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -107,9 +107,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -143,9 +143,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -179,9 +179,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -215,9 +215,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -251,9 +251,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -287,9 +287,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -323,9 +323,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -359,9 +359,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -395,9 +395,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -431,9 +431,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -467,9 +467,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -503,9 +503,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -539,9 +539,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -575,9 +575,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -611,9 +611,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -647,9 +647,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -683,9 +683,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -719,9 +719,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -755,9 +755,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -791,9 +791,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -827,9 +827,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -863,9 +863,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -899,9 +899,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -935,9 +935,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -971,9 +971,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1007,9 +1007,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1043,9 +1043,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1079,9 +1079,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1115,9 +1115,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1151,9 +1151,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1187,9 +1187,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1223,9 +1223,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1259,9 +1259,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1295,9 +1295,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1331,9 +1331,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1367,9 +1367,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1403,9 +1403,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1439,9 +1439,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1475,9 +1475,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1511,9 +1511,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1547,9 +1547,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1583,9 +1583,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1619,9 +1619,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1655,9 +1655,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1691,9 +1691,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1727,9 +1727,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1763,9 +1763,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1799,9 +1799,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1835,9 +1835,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1871,9 +1871,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1907,9 +1907,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1943,9 +1943,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1979,9 +1979,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2015,9 +2015,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2051,9 +2051,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2087,9 +2087,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2123,9 +2123,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2159,9 +2159,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2195,9 +2195,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2231,9 +2231,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2267,9 +2267,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2303,9 +2303,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2339,9 +2339,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2375,9 +2375,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2411,9 +2411,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2447,9 +2447,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2483,9 +2483,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2519,9 +2519,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2555,9 +2555,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2591,9 +2591,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2627,9 +2627,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2663,9 +2663,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2699,9 +2699,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2735,9 +2735,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2771,9 +2771,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2807,9 +2807,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2843,9 +2843,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2879,9 +2879,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2915,9 +2915,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2951,9 +2951,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2987,9 +2987,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3023,9 +3023,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3059,9 +3059,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3095,9 +3095,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3131,9 +3131,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3167,9 +3167,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3203,9 +3203,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3239,9 +3239,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3275,9 +3275,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3311,9 +3311,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3347,9 +3347,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3383,9 +3383,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3419,9 +3419,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3455,9 +3455,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3491,9 +3491,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3527,9 +3527,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3563,9 +3563,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3599,9 +3599,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3635,9 +3635,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3671,9 +3671,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3707,9 +3707,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3743,9 +3743,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3779,9 +3779,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3815,9 +3815,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3851,9 +3851,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3887,9 +3887,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3923,9 +3923,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3959,9 +3959,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3995,9 +3995,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4031,9 +4031,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4067,9 +4067,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4103,9 +4103,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4139,9 +4139,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4175,9 +4175,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4211,9 +4211,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4247,9 +4247,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4283,9 +4283,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4319,9 +4319,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4355,9 +4355,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4391,9 +4391,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4427,9 +4427,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4463,9 +4463,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4499,9 +4499,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4535,9 +4535,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4571,9 +4571,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4607,9 +4607,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4643,9 +4643,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4679,9 +4679,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4715,9 +4715,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4751,9 +4751,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4787,9 +4787,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4823,9 +4823,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4859,9 +4859,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4895,9 +4895,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4931,9 +4931,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4967,9 +4967,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5003,9 +5003,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5039,9 +5039,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5075,9 +5075,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5111,9 +5111,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5147,9 +5147,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5183,9 +5183,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5219,9 +5219,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5255,9 +5255,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5291,9 +5291,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5327,9 +5327,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5363,9 +5363,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5399,9 +5399,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5435,9 +5435,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5471,9 +5471,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5507,9 +5507,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5543,9 +5543,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5579,9 +5579,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5615,9 +5615,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5651,9 +5651,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5687,9 +5687,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5723,9 +5723,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5759,9 +5759,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5795,9 +5795,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5831,9 +5831,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5867,9 +5867,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5903,9 +5903,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5939,9 +5939,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -5975,9 +5975,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6011,9 +6011,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6047,9 +6047,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6083,9 +6083,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6119,9 +6119,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6155,9 +6155,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6191,9 +6191,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6227,9 +6227,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6263,9 +6263,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6299,9 +6299,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6335,9 +6335,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6371,9 +6371,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6407,9 +6407,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -6443,9 +6443,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-41</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:colOff>-100</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -7055,7 +7055,7 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7082,7 +7082,7 @@
       <b val="true"/>
       <sz val="21"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7090,7 +7090,7 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7098,28 +7098,28 @@
       <b val="true"/>
       <sz val="15"/>
       <color rgb="FF008000"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF243746"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF667085"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <color rgb="FF142D43"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -7139,7 +7139,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7147,7 +7147,7 @@
       <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7159,7 +7159,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF202020"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7174,12 +7174,20 @@
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF202020"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7195,17 +7203,23 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF28566F"/>
-        <bgColor rgb="FF243746"/>
+        <bgColor rgb="FF176443"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F5FF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF6F9FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF2F5"/>
+        <bgColor rgb="FFE6F4EC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -7218,6 +7232,15 @@
       <right/>
       <top/>
       <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAEC5CE"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -7250,7 +7273,7 @@
       <protection locked="false" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7323,6 +7346,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7333,7 +7360,7 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7381,6 +7408,28 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF176443"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFA12232"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE9EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -7398,28 +7447,28 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF287F8E"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFAEC5CE"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF0F5FF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF6F9FB"/>
+      <rgbColor rgb="FFE6F4EC"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF176443"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFEAF2F5"/>
+      <rgbColor rgb="FFF0F5FF"/>
+      <rgbColor rgb="FFFCE9EC"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -7436,7 +7485,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF202020"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFA12232"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF28566F"/>
       <rgbColor rgb="FF243746"/>
@@ -7463,9 +7512,9 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1800" b="1" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="1200" b="1" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="142D43"/>
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
@@ -7616,11 +7665,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="70091823"/>
-        <c:axId val="69037462"/>
+        <c:axId val="16272943"/>
+        <c:axId val="69783871"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70091823"/>
+        <c:axId val="16272943"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7653,7 +7702,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69037462"/>
+        <c:crossAx val="69783871"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7661,7 +7710,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69037462"/>
+        <c:axId val="69783871"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7737,7 +7786,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70091823"/>
+        <c:crossAx val="16272943"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7751,11 +7800,11 @@
     <c:dispBlanksAs val="gap"/>
   </c:chart>
   <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="F6F9FB"/>
+    </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -7779,9 +7828,9 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1800" b="1" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="1200" b="1" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="142D43"/>
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
@@ -7937,11 +7986,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96677331"/>
-        <c:axId val="66962104"/>
+        <c:axId val="52017761"/>
+        <c:axId val="70453521"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96677331"/>
+        <c:axId val="52017761"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7974,7 +8023,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66962104"/>
+        <c:crossAx val="70453521"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7982,7 +8031,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66962104"/>
+        <c:axId val="70453521"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8058,7 +8107,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96677331"/>
+        <c:crossAx val="52017761"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8072,11 +8121,11 @@
     <c:dispBlanksAs val="gap"/>
   </c:chart>
   <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="F6F9FB"/>
+    </a:solidFill>
     <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:round/>
+      <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -8534,10 +8583,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>380520</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>237600</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>514080</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>285120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -8545,8 +8594,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="5200560"/>
-        <a:ext cx="5817240" cy="2714040"/>
+        <a:off x="0" y="6000840"/>
+        <a:ext cx="5407560" cy="2856960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8558,16 +8607,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>380520</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>237600</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>418680</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>285120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -8575,8 +8624,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="8915400"/>
-        <a:ext cx="5817240" cy="2714040"/>
+        <a:off x="7390080" y="6000840"/>
+        <a:ext cx="5412240" cy="2856960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8771,17 +8820,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF287F8E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8794,7 +8844,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -8805,7 +8855,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -8817,7 +8867,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -8827,7 +8877,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>2</v>
       </c>
@@ -8836,7 +8886,7 @@
         <v>base</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>3</v>
       </c>
@@ -8845,7 +8895,7 @@
         <v>0.787126299267323</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>4</v>
       </c>
@@ -8854,7 +8904,7 @@
         <v>697702091.007811</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>5</v>
       </c>
@@ -8863,7 +8913,7 @@
         <v>374000000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -8875,7 +8925,7 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -8885,7 +8935,7 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -8895,7 +8945,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
@@ -8907,7 +8957,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -8917,7 +8967,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -8927,7 +8977,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -8958,17 +9008,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF287F8E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I73"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -8981,7 +9032,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -8992,7 +9043,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
@@ -9008,7 +9059,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>11</v>
       </c>
@@ -9019,7 +9070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>13</v>
       </c>
@@ -9030,7 +9081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>14</v>
       </c>
@@ -9041,7 +9092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>15</v>
       </c>
@@ -9052,7 +9103,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>17</v>
       </c>
@@ -9061,7 +9112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>19</v>
       </c>
@@ -9072,7 +9123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>22</v>
       </c>
@@ -9081,7 +9132,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
@@ -9093,7 +9144,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -9103,7 +9154,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -9116,7 +9167,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>25</v>
       </c>
@@ -9124,7 +9175,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>26</v>
       </c>
@@ -9132,7 +9183,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>27</v>
       </c>
@@ -9140,7 +9191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>28</v>
       </c>
@@ -9148,7 +9199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="12" t="n">
         <v>2027</v>
       </c>
@@ -9171,7 +9222,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>29</v>
       </c>
@@ -9200,7 +9251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>31</v>
       </c>
@@ -9229,7 +9280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
         <v>33</v>
       </c>
@@ -9258,7 +9309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
         <v>35</v>
       </c>
@@ -9287,7 +9338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
         <v>36</v>
       </c>
@@ -9316,7 +9367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
         <v>38</v>
       </c>
@@ -9345,7 +9396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
         <v>39</v>
       </c>
@@ -9374,7 +9425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
         <v>40</v>
       </c>
@@ -9403,7 +9454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>41</v>
       </c>
@@ -9432,7 +9483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
         <v>42</v>
       </c>
@@ -9461,7 +9512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
         <v>43</v>
       </c>
@@ -9490,7 +9541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>44</v>
       </c>
@@ -9503,7 +9554,7 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
         <v>25</v>
       </c>
@@ -9511,7 +9562,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
         <v>26</v>
       </c>
@@ -9519,7 +9570,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
         <v>27</v>
       </c>
@@ -9527,7 +9578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
         <v>28</v>
       </c>
@@ -9535,7 +9586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C43" s="12" t="n">
         <v>2027</v>
       </c>
@@ -9558,7 +9609,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
         <v>29</v>
       </c>
@@ -9587,7 +9638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
         <v>31</v>
       </c>
@@ -9616,7 +9667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
         <v>33</v>
       </c>
@@ -9645,7 +9696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
         <v>35</v>
       </c>
@@ -9674,7 +9725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
         <v>36</v>
       </c>
@@ -9703,7 +9754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
         <v>38</v>
       </c>
@@ -9732,7 +9783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
         <v>39</v>
       </c>
@@ -9761,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
         <v>40</v>
       </c>
@@ -9790,7 +9841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
         <v>41</v>
       </c>
@@ -9819,7 +9870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
         <v>42</v>
       </c>
@@ -9848,7 +9899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
         <v>43</v>
       </c>
@@ -9877,7 +9928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>45</v>
       </c>
@@ -9890,7 +9941,7 @@
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
     </row>
-    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
         <v>25</v>
       </c>
@@ -9898,7 +9949,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
         <v>26</v>
       </c>
@@ -9906,7 +9957,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
         <v>27</v>
       </c>
@@ -9914,7 +9965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
         <v>28</v>
       </c>
@@ -9922,7 +9973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C62" s="12" t="n">
         <v>2027</v>
       </c>
@@ -9945,7 +9996,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
         <v>29</v>
       </c>
@@ -9974,7 +10025,7 @@
         <v>12415.7</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
         <v>31</v>
       </c>
@@ -10003,7 +10054,7 @@
         <v>76512</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
         <v>33</v>
       </c>
@@ -10032,7 +10083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
         <v>35</v>
       </c>
@@ -10061,7 +10112,7 @@
         <v>26066.1</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
         <v>36</v>
       </c>
@@ -10090,7 +10141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
         <v>38</v>
       </c>
@@ -10119,7 +10170,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
         <v>39</v>
       </c>
@@ -10148,7 +10199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
         <v>40</v>
       </c>
@@ -10177,7 +10228,7 @@
         <v>93600000</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
         <v>41</v>
       </c>
@@ -10206,7 +10257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
         <v>42</v>
       </c>
@@ -10235,7 +10286,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
         <v>43</v>
       </c>
@@ -10281,7 +10332,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter>&amp;Lasx-mlx | Assumptions&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -10297,19 +10348,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF142D43"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I79"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -10322,7 +10376,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -10333,7 +10387,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>47</v>
       </c>
@@ -10346,7 +10400,7 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>48</v>
       </c>
@@ -10375,7 +10429,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>57</v>
       </c>
@@ -10404,7 +10458,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
         <v>63</v>
       </c>
@@ -10433,7 +10487,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>64</v>
       </c>
@@ -10462,7 +10516,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
         <v>65</v>
       </c>
@@ -10489,7 +10543,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>67</v>
       </c>
@@ -10518,7 +10572,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>69</v>
       </c>
@@ -10547,7 +10601,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>72</v>
       </c>
@@ -10576,7 +10630,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>73</v>
       </c>
@@ -10605,7 +10659,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
         <v>74</v>
       </c>
@@ -10632,7 +10686,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
         <v>78</v>
       </c>
@@ -10659,7 +10713,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
         <v>74</v>
       </c>
@@ -10686,7 +10740,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
         <v>74</v>
       </c>
@@ -10713,7 +10767,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
         <v>83</v>
       </c>
@@ -10742,7 +10796,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
         <v>83</v>
       </c>
@@ -10771,7 +10825,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
         <v>85</v>
       </c>
@@ -10800,7 +10854,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
         <v>85</v>
       </c>
@@ -10829,7 +10883,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
         <v>86</v>
       </c>
@@ -10858,7 +10912,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
         <v>87</v>
       </c>
@@ -10887,7 +10941,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
         <v>88</v>
       </c>
@@ -10916,7 +10970,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
         <v>90</v>
       </c>
@@ -10945,7 +10999,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
         <v>91</v>
       </c>
@@ -10974,7 +11028,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
         <v>57</v>
       </c>
@@ -11003,7 +11057,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
         <v>93</v>
       </c>
@@ -11032,7 +11086,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
         <v>95</v>
       </c>
@@ -11061,7 +11115,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
         <v>95</v>
       </c>
@@ -11090,7 +11144,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
         <v>98</v>
       </c>
@@ -11119,7 +11173,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
         <v>98</v>
       </c>
@@ -11148,7 +11202,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
         <v>99</v>
       </c>
@@ -11177,7 +11231,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
         <v>99</v>
       </c>
@@ -11206,7 +11260,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
         <v>100</v>
       </c>
@@ -11235,7 +11289,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
         <v>100</v>
       </c>
@@ -11264,7 +11318,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
         <v>101</v>
       </c>
@@ -11293,7 +11347,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
         <v>101</v>
       </c>
@@ -11322,7 +11376,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
         <v>102</v>
       </c>
@@ -11351,7 +11405,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
         <v>102</v>
       </c>
@@ -11380,7 +11434,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
         <v>103</v>
       </c>
@@ -11409,7 +11463,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
         <v>103</v>
       </c>
@@ -11438,7 +11492,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
         <v>104</v>
       </c>
@@ -11467,7 +11521,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
         <v>104</v>
       </c>
@@ -11496,7 +11550,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
         <v>57</v>
       </c>
@@ -11525,7 +11579,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
         <v>106</v>
       </c>
@@ -11554,7 +11608,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
         <v>106</v>
       </c>
@@ -11583,7 +11637,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
         <v>107</v>
       </c>
@@ -11612,7 +11666,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
         <v>107</v>
       </c>
@@ -11641,7 +11695,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
         <v>108</v>
       </c>
@@ -11670,7 +11724,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
         <v>108</v>
       </c>
@@ -11699,7 +11753,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
         <v>109</v>
       </c>
@@ -11728,7 +11782,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
         <v>109</v>
       </c>
@@ -11757,7 +11811,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
         <v>110</v>
       </c>
@@ -11786,7 +11840,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
         <v>110</v>
       </c>
@@ -11815,7 +11869,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
         <v>111</v>
       </c>
@@ -11844,7 +11898,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
         <v>111</v>
       </c>
@@ -11873,7 +11927,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
         <v>63</v>
       </c>
@@ -11902,7 +11956,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
         <v>64</v>
       </c>
@@ -11931,7 +11985,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
         <v>112</v>
       </c>
@@ -11960,7 +12014,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
         <v>112</v>
       </c>
@@ -11989,7 +12043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
         <v>113</v>
       </c>
@@ -12018,7 +12072,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
         <v>113</v>
       </c>
@@ -12047,7 +12101,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
         <v>114</v>
       </c>
@@ -12076,7 +12130,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
         <v>114</v>
       </c>
@@ -12105,7 +12159,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
         <v>115</v>
       </c>
@@ -12134,7 +12188,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
         <v>115</v>
       </c>
@@ -12163,7 +12217,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="s">
         <v>69</v>
       </c>
@@ -12192,7 +12246,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="13" t="s">
         <v>72</v>
       </c>
@@ -12221,7 +12275,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
         <v>73</v>
       </c>
@@ -12250,7 +12304,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
         <v>116</v>
       </c>
@@ -12279,7 +12333,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="13" t="s">
         <v>116</v>
       </c>
@@ -12308,7 +12362,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="13" t="s">
         <v>117</v>
       </c>
@@ -12337,7 +12391,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="13" t="s">
         <v>117</v>
       </c>
@@ -12366,7 +12420,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="13" t="s">
         <v>118</v>
       </c>
@@ -12395,7 +12449,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="13" t="s">
         <v>118</v>
       </c>
@@ -12424,7 +12478,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="13" t="s">
         <v>119</v>
       </c>
@@ -12453,7 +12507,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="13" t="s">
         <v>119</v>
       </c>
@@ -12577,17 +12631,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF142D43"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>120</v>
       </c>
@@ -12600,7 +12655,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -12611,7 +12666,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>25</v>
       </c>
@@ -12620,7 +12675,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>26</v>
       </c>
@@ -12629,7 +12684,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>27</v>
       </c>
@@ -12638,7 +12693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>121</v>
       </c>
@@ -12647,7 +12702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>122</v>
       </c>
@@ -12656,7 +12711,7 @@
         <v>imputed_production</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
         <v>123</v>
       </c>
@@ -12689,7 +12744,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>124</v>
       </c>
@@ -12725,7 +12780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>31</v>
       </c>
@@ -12761,7 +12816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>33</v>
       </c>
@@ -12797,7 +12852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>35</v>
       </c>
@@ -12833,7 +12888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>36</v>
       </c>
@@ -12869,7 +12924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>38</v>
       </c>
@@ -12905,7 +12960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>39</v>
       </c>
@@ -12941,7 +12996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
         <v>40</v>
       </c>
@@ -12977,7 +13032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
         <v>41</v>
       </c>
@@ -13013,7 +13068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>42</v>
       </c>
@@ -13049,7 +13104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>43</v>
       </c>
@@ -13085,7 +13140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
         <v>126</v>
       </c>
@@ -13121,7 +13176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
         <v>127</v>
       </c>
@@ -13157,7 +13212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
         <v>128</v>
       </c>
@@ -13193,7 +13248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
         <v>129</v>
       </c>
@@ -13229,7 +13284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
         <v>130</v>
       </c>
@@ -13265,7 +13320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
         <v>131</v>
       </c>
@@ -13301,7 +13356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
         <v>132</v>
       </c>
@@ -13337,115 +13392,115 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
         <v>133</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="18" t="n">
         <f aca="false">Operating!$C$29*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0)</f>
         <v>94448244.9</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="18" t="n">
         <f aca="false">Operating!$D$29*Operating!$B$5-Operating!$D$20+IF(2=Operating!$B$7,Operating!$B$6,0)</f>
         <v>94448244.9</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="18" t="n">
         <f aca="false">Operating!$E$29*Operating!$B$5-Operating!$E$20+IF(3=Operating!$B$7,Operating!$B$6,0)</f>
         <v>94448244.9</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="18" t="n">
         <f aca="false">Operating!$F$29*Operating!$B$5-Operating!$F$20+IF(4=Operating!$B$7,Operating!$B$6,0)</f>
         <v>94448244.9</v>
       </c>
-      <c r="G30" s="14" t="n">
+      <c r="G30" s="18" t="n">
         <f aca="false">Operating!$G$29*Operating!$B$5-Operating!$G$20+IF(5=Operating!$B$7,Operating!$B$6,0)</f>
         <v>44448244.9</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="H30" s="18" t="n">
         <f aca="false">Operating!$H$29*Operating!$B$5-Operating!$H$20+IF(6=Operating!$B$7,Operating!$B$6,0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="14" t="n">
+      <c r="I30" s="18" t="n">
         <f aca="false">Operating!$I$29*Operating!$B$5-Operating!$I$20+IF(7=Operating!$B$7,Operating!$B$6,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
         <v>134</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="18" t="n">
         <f aca="false">Operating!$C$30/(1+Operating!$B$4)^1</f>
         <v>85862040.8181818</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="18" t="n">
         <f aca="false">Operating!$D$30/(1+Operating!$B$4)^2</f>
         <v>78056400.7438016</v>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="18" t="n">
         <f aca="false">Operating!$E$30/(1+Operating!$B$4)^3</f>
         <v>70960364.3125469</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F31" s="18" t="n">
         <f aca="false">Operating!$F$30/(1+Operating!$B$4)^4</f>
         <v>64509422.1023154</v>
       </c>
-      <c r="G31" s="14" t="n">
+      <c r="G31" s="18" t="n">
         <f aca="false">Operating!$G$30/(1+Operating!$B$4)^5</f>
         <v>27598863.0309653</v>
       </c>
-      <c r="H31" s="14" t="n">
+      <c r="H31" s="18" t="n">
         <f aca="false">Operating!$H$30/(1+Operating!$B$4)^6</f>
         <v>0</v>
       </c>
-      <c r="I31" s="14" t="n">
+      <c r="I31" s="18" t="n">
         <f aca="false">Operating!$I$30/(1+Operating!$B$4)^7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
         <v>135</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C32" s="18" t="n">
         <f aca="false">Assumptions!$B$7+Operating!$C$30</f>
         <v>468448244.9</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D32" s="18" t="n">
         <f aca="false">Operating!$C$32+Operating!$D$30</f>
         <v>562896489.8</v>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E32" s="18" t="n">
         <f aca="false">Operating!$D$32+Operating!$E$30</f>
         <v>657344734.7</v>
       </c>
-      <c r="F32" s="14" t="n">
+      <c r="F32" s="18" t="n">
         <f aca="false">Operating!$E$32+Operating!$F$30</f>
         <v>751792979.6</v>
       </c>
-      <c r="G32" s="14" t="n">
+      <c r="G32" s="18" t="n">
         <f aca="false">Operating!$F$32+Operating!$G$30</f>
         <v>796241224.5</v>
       </c>
-      <c r="H32" s="14" t="n">
+      <c r="H32" s="18" t="n">
         <f aca="false">Operating!$G$32+Operating!$H$30</f>
         <v>796241224.5</v>
       </c>
-      <c r="I32" s="14" t="n">
+      <c r="I32" s="18" t="n">
         <f aca="false">Operating!$H$32+Operating!$I$30</f>
         <v>796241224.5</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
         <v>136</v>
       </c>
@@ -13458,7 +13513,7 @@
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
     </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -13476,7 +13531,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter>&amp;Lasx-mlx | Operating&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -13487,17 +13542,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF142D43"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>137</v>
       </c>
@@ -13510,7 +13566,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -13521,7 +13577,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>138</v>
       </c>
@@ -13533,7 +13589,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>11</v>
       </c>
@@ -13545,7 +13601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>14</v>
       </c>
@@ -13557,7 +13613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>13</v>
       </c>
@@ -13569,7 +13625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>139</v>
       </c>
@@ -13581,7 +13637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>15</v>
       </c>
@@ -13593,7 +13649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>140</v>
       </c>
@@ -13605,7 +13661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>141</v>
       </c>
@@ -13617,7 +13673,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>142</v>
       </c>
@@ -13626,7 +13682,7 @@
         <v>Unavailable</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>143</v>
       </c>
@@ -13635,7 +13691,7 @@
         <v>Unavailable</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
         <v>144</v>
       </c>
@@ -13645,7 +13701,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -13653,7 +13709,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -13679,17 +13735,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF142D43"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
@@ -13702,7 +13759,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -13713,7 +13770,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>146</v>
       </c>
@@ -13723,7 +13780,7 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -13731,7 +13788,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C7" s="16" t="n">
         <f aca="false">MAX(0,Operating!$B$4+(-0.02))</f>
         <v>0.08</v>
@@ -13745,7 +13802,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="14" t="n">
         <v>0.8</v>
       </c>
@@ -13762,7 +13819,7 @@
         <v>0.565454109640298</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="14" t="n">
         <v>1</v>
       </c>
@@ -13779,7 +13836,7 @@
         <v>0.770323737886184</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="14" t="n">
         <v>1.2</v>
       </c>
@@ -13796,12 +13853,12 @@
         <v>0.975193366132069</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
         <v>148</v>
       </c>
@@ -13834,7 +13891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
         <v>149</v>
       </c>
@@ -13867,7 +13924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
         <v>150</v>
       </c>
@@ -13900,7 +13957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
         <v>151</v>
       </c>
@@ -13933,7 +13990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
         <v>152</v>
       </c>
@@ -13966,7 +14023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
         <v>153</v>
       </c>
@@ -13999,7 +14056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
         <v>154</v>
       </c>
@@ -14032,7 +14089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
         <v>155</v>
       </c>
@@ -14065,7 +14122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
         <v>156</v>
       </c>
@@ -14128,17 +14185,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF142D43"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>157</v>
       </c>
@@ -14151,7 +14209,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14162,7 +14220,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>158</v>
       </c>
@@ -14171,7 +14229,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>159</v>
       </c>
@@ -14180,7 +14238,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>160</v>
       </c>
@@ -14189,7 +14247,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>161</v>
       </c>
@@ -14198,7 +14256,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>162</v>
       </c>
@@ -14207,7 +14265,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>163</v>
       </c>
@@ -14216,7 +14274,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>164</v>
       </c>
@@ -14226,7 +14284,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -14234,7 +14292,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -14247,6 +14305,14 @@
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A13:F15"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:B10">
+    <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="PASS" dxfId="6">
+      <formula>NOT(ISERROR(SEARCH("PASS",B5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="FAIL" dxfId="7">
+      <formula>NOT(ISERROR(SEARCH("FAIL",B5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -14260,17 +14326,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF142D43"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I85"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
@@ -14283,7 +14350,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14294,7 +14361,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>166</v>
       </c>
@@ -14306,7 +14373,7 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -14316,7 +14383,7 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -14326,7 +14393,7 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>167</v>
       </c>
@@ -14338,7 +14405,7 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -14348,7 +14415,7 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -14358,7 +14425,7 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>168</v>
       </c>
@@ -14370,7 +14437,7 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -14380,7 +14447,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -14390,7 +14457,7 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>169</v>
       </c>
@@ -14402,7 +14469,7 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -14412,7 +14479,7 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -14422,7 +14489,7 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>170</v>
       </c>
@@ -14434,7 +14501,7 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -14444,7 +14511,7 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -14454,7 +14521,7 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>171</v>
       </c>
@@ -14466,7 +14533,7 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -14476,7 +14543,7 @@
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -14486,7 +14553,7 @@
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>172</v>
       </c>
@@ -14498,7 +14565,7 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -14508,7 +14575,7 @@
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -14518,7 +14585,7 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
         <v>173</v>
       </c>
@@ -14530,7 +14597,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>174</v>
       </c>
@@ -14542,7 +14609,7 @@
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -14552,7 +14619,7 @@
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
     </row>
-    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -14562,7 +14629,7 @@
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
     </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>175</v>
       </c>
@@ -14574,7 +14641,7 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
     </row>
-    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -14584,7 +14651,7 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
     </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -14594,7 +14661,7 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
     </row>
-    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>176</v>
       </c>
@@ -14606,7 +14673,7 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
     </row>
-    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -14616,7 +14683,7 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
     </row>
-    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -14626,7 +14693,7 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
     </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>177</v>
       </c>
@@ -14638,7 +14705,7 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
     </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -14648,7 +14715,7 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -14658,7 +14725,7 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
     </row>
-    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>178</v>
       </c>
@@ -14670,7 +14737,7 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
     </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -14680,7 +14747,7 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
     </row>
-    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -14690,7 +14757,7 @@
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
     </row>
-    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>179</v>
       </c>
@@ -14702,7 +14769,7 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
     </row>
-    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -14712,7 +14779,7 @@
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
     </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -14722,7 +14789,7 @@
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
     </row>
-    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>180</v>
       </c>
@@ -14734,7 +14801,7 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
     </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -14744,7 +14811,7 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
     </row>
-    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -14754,7 +14821,7 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
     </row>
-    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>181</v>
       </c>
@@ -14766,7 +14833,7 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
     </row>
-    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -14776,7 +14843,7 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
     </row>
-    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -14786,7 +14853,7 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
     </row>
-    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>182</v>
       </c>
@@ -14798,7 +14865,7 @@
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
     </row>
-    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -14808,7 +14875,7 @@
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
     </row>
-    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -14818,7 +14885,7 @@
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
     </row>
-    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>183</v>
       </c>
@@ -14830,7 +14897,7 @@
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
     </row>
-    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -14840,7 +14907,7 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
     </row>
-    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -14850,7 +14917,7 @@
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
     </row>
-    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>184</v>
       </c>
@@ -14862,7 +14929,7 @@
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
     </row>
-    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -14872,7 +14939,7 @@
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
     </row>
-    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -14882,7 +14949,7 @@
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
     </row>
-    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>185</v>
       </c>
@@ -14894,7 +14961,7 @@
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
     </row>
-    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -14904,7 +14971,7 @@
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
     </row>
-    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -14914,7 +14981,7 @@
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
     </row>
-    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
         <v>186</v>
       </c>
@@ -14926,7 +14993,7 @@
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
     </row>
-    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -14936,7 +15003,7 @@
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
     </row>
-    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -14973,7 +15040,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter>&amp;Lasx-mlx | Readme&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -14984,47 +15051,48 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF142D43"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>193</v>
       </c>

--- a/examples/mlx/model.xlsx
+++ b/examples/mlx/model.xlsx
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Assumptions!$A$1:$I$74</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Assumptions!$1:$2</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Checks!$A$1:$I$46</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Historical!$A$1:$I$79</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Historical!$1:$6</definedName>
@@ -27,7 +28,7 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Operating!$A$1:$I$36</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Readme!$A$1:$H$89</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Sensitivities!$A$1:$I$46</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$I$36</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$I$33</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Valuation!$A$1:$I$46</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -71,7 +72,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -107,7 +108,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -143,7 +144,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -179,7 +180,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -215,7 +216,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -251,7 +252,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -287,7 +288,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -323,7 +324,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -359,7 +360,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -395,7 +396,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -431,7 +432,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -467,7 +468,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -503,7 +504,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -539,7 +540,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -575,7 +576,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -611,7 +612,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -647,7 +648,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -683,7 +684,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -719,7 +720,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -755,7 +756,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -791,7 +792,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -827,7 +828,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -863,7 +864,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -899,7 +900,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -935,7 +936,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -971,7 +972,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1007,7 +1008,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1043,7 +1044,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1079,7 +1080,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1115,7 +1116,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1151,7 +1152,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1187,7 +1188,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1223,7 +1224,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1259,7 +1260,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1295,7 +1296,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1331,7 +1332,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1367,7 +1368,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1403,7 +1404,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1439,7 +1440,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1475,7 +1476,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1511,7 +1512,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1547,7 +1548,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1583,7 +1584,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1619,7 +1620,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1655,7 +1656,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1691,7 +1692,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1727,7 +1728,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1763,7 +1764,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1799,7 +1800,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1835,7 +1836,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1871,7 +1872,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1907,7 +1908,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1943,7 +1944,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -1979,7 +1980,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2015,7 +2016,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2051,7 +2052,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2087,7 +2088,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2123,7 +2124,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2159,7 +2160,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2195,7 +2196,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2231,7 +2232,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2267,7 +2268,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2303,7 +2304,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2339,7 +2340,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2375,7 +2376,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2411,7 +2412,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2447,7 +2448,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2483,7 +2484,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2519,7 +2520,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2555,7 +2556,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2591,7 +2592,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2627,7 +2628,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2663,7 +2664,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2699,7 +2700,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2735,7 +2736,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2771,7 +2772,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2807,7 +2808,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2843,7 +2844,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2879,7 +2880,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2915,7 +2916,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2951,7 +2952,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -2987,7 +2988,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3023,7 +3024,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3059,7 +3060,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3095,7 +3096,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3131,7 +3132,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3167,7 +3168,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3203,7 +3204,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3239,7 +3240,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3275,7 +3276,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3311,7 +3312,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3347,7 +3348,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3383,7 +3384,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3419,7 +3420,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3455,7 +3456,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3491,7 +3492,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3527,7 +3528,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3563,7 +3564,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3599,7 +3600,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3635,7 +3636,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3671,7 +3672,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3707,7 +3708,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3743,7 +3744,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3779,7 +3780,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3815,7 +3816,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3851,7 +3852,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3887,7 +3888,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3923,7 +3924,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3959,7 +3960,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -3995,7 +3996,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4031,7 +4032,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4067,7 +4068,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4103,7 +4104,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4139,7 +4140,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4175,7 +4176,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4211,7 +4212,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4247,7 +4248,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4283,7 +4284,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4319,7 +4320,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4355,7 +4356,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4391,7 +4392,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4427,7 +4428,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4463,7 +4464,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4499,7 +4500,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4535,7 +4536,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4571,7 +4572,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4607,7 +4608,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4643,7 +4644,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4679,7 +4680,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4715,7 +4716,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4751,7 +4752,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4787,7 +4788,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4823,7 +4824,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4859,7 +4860,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4895,7 +4896,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4931,7 +4932,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -4967,7 +4968,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5003,7 +5004,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5039,7 +5040,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5075,7 +5076,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5111,7 +5112,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5147,7 +5148,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5183,7 +5184,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5219,7 +5220,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5255,7 +5256,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5291,7 +5292,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5327,7 +5328,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5363,7 +5364,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5399,7 +5400,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5435,7 +5436,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5471,7 +5472,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5507,7 +5508,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5543,7 +5544,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5579,7 +5580,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5615,7 +5616,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5651,7 +5652,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5687,7 +5688,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5723,7 +5724,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5759,7 +5760,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5795,7 +5796,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5831,7 +5832,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5867,7 +5868,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5903,7 +5904,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5939,7 +5940,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -5975,7 +5976,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6011,7 +6012,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6047,7 +6048,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6083,7 +6084,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6119,7 +6120,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6155,7 +6156,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6191,7 +6192,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6227,7 +6228,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6263,7 +6264,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6299,7 +6300,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6335,7 +6336,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6371,7 +6372,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6407,7 +6408,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6443,7 +6444,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>-100</xdr:colOff>
+                <xdr:colOff>-68</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
@@ -6458,33 +6459,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="194">
-  <si>
-    <t xml:space="preserve">asx-mlx  /  Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILLUSTRATIVE SENSITIVITY — not an actionable valuation</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="193">
+  <si>
+    <t xml:space="preserve">ASX:MLX  /  Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative scenarios | Review assumptions before using these values</t>
   </si>
   <si>
     <t xml:space="preserve">Active scenario</t>
   </si>
   <si>
-    <t xml:space="preserve">Model value per share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum illustrative cash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Markdown is the main research narrative. Use this workbook to inspect and edit detailed assumptions; recalculate in Excel or LibreOffice, save, then import to publish a validated snapshot back to the research memo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Known limitations: ILLUSTRATIVE IMPUTED-REVENUE SENSITIVITY ONLY. This is not an actionable fair-value estimate or an investment recommendation. • Production is used solely as the company-style imputed-revenue proxy (100% produced tin sold/paid); it is NOT reported payable sales. The workbook labels it production_tonnes_proxy. Realized payable sales, inventory, settlement timing and revenue must replace this proxy before valuation. See Readme for the full limitations register.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asx-mlx  /  Assumptions</t>
+    <t xml:space="preserve">Model value per share (AUD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity value (AUD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum cash (AUD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with the investment report for the full story. Choose a scenario on Assumptions, then explore its cash flows, valuation and sensitivities here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These figures illustrate the supplied assumptions, not a predicted share price. The cash chart excludes financing and dividends. Readme explains the limitations and evidence still needed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASX:MLX  /  Assumptions</t>
   </si>
   <si>
     <t xml:space="preserve">base</t>
@@ -6598,7 +6599,7 @@
     <t xml:space="preserve">BULL / whole_operation</t>
   </si>
   <si>
-    <t xml:space="preserve">asx-mlx  /  Historical</t>
+    <t xml:space="preserve">ASX:MLX  /  Historical</t>
   </si>
   <si>
     <t xml:space="preserve">Source-linked reported facts. Historical coverage may be incomplete; no integrated statements are inferred.</t>
@@ -6631,7 +6632,7 @@
     <t xml:space="preserve">Page</t>
   </si>
   <si>
-    <t xml:space="preserve">cash_and_cash_equivalents</t>
+    <t xml:space="preserve">Cash and cash equivalents</t>
   </si>
   <si>
     <t xml:space="preserve">2025-12-31</t>
@@ -6649,25 +6650,25 @@
     <t xml:space="preserve">25</t>
   </si>
   <si>
-    <t xml:space="preserve">current_interest_bearing_liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noncurrent_interest_bearing_liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">issued_ordinary_shares</t>
+    <t xml:space="preserve">Current interest bearing liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noncurrent interest bearing liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issued ordinary shares</t>
   </si>
   <si>
     <t xml:space="preserve">62</t>
   </si>
   <si>
-    <t xml:space="preserve">rehabilitation_provision_present_value</t>
+    <t xml:space="preserve">Rehabilitation provision present value</t>
   </si>
   <si>
     <t xml:space="preserve">60</t>
   </si>
   <si>
-    <t xml:space="preserve">net_operating_cash_flow</t>
+    <t xml:space="preserve">Net operating cash flow</t>
   </si>
   <si>
     <t xml:space="preserve">FY2025</t>
@@ -6676,13 +6677,13 @@
     <t xml:space="preserve">26</t>
   </si>
   <si>
-    <t xml:space="preserve">cash_paid_property_plant_equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cash_paid_mine_properties_development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tin_in_concentrate_produced</t>
+    <t xml:space="preserve">Cash paid property plant equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash paid mine properties development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tin in concentrate produced</t>
   </si>
   <si>
     <t xml:space="preserve">tonnes_tin</t>
@@ -6694,7 +6695,7 @@
     <t xml:space="preserve">9</t>
   </si>
   <si>
-    <t xml:space="preserve">ownership_interest</t>
+    <t xml:space="preserve">Ownership interest</t>
   </si>
   <si>
     <t xml:space="preserve">2026-Q2</t>
@@ -6709,43 +6710,43 @@
     <t xml:space="preserve">TTM-ended-2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">imputed_tin_price</t>
+    <t xml:space="preserve">Imputed tin price</t>
   </si>
   <si>
     <t xml:space="preserve">AUD_per_tonne_tin</t>
   </si>
   <si>
-    <t xml:space="preserve">c1_cash_production_cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imputed_sales_and_marketing_cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all_in_sustaining_cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capital_expenditure</t>
+    <t xml:space="preserve">C1 cash production cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imputed sales and marketing cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All in sustaining cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital expenditure</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">sustaining_capital_expenditure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">project_capital_expenditure</t>
+    <t xml:space="preserve">Sustaining capital expenditure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project capital expenditure</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">corporate_costs</t>
+    <t xml:space="preserve">Corporate costs</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">revenue</t>
+    <t xml:space="preserve">Revenue</t>
   </si>
   <si>
     <t xml:space="preserve">24</t>
@@ -6754,73 +6755,73 @@
     <t xml:space="preserve">FY2024</t>
   </si>
   <si>
-    <t xml:space="preserve">cost_of_sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gross_profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">general_and_administrative_expenses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">finance_costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">profit_before_tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income_tax_expense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">net_income</t>
+    <t xml:space="preserve">Cost of sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General and administrative expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit before tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income tax expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net income</t>
   </si>
   <si>
     <t xml:space="preserve">2024-12-31</t>
   </si>
   <si>
-    <t xml:space="preserve">trade_and_other_receivables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inventories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_current_assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_noncurrent_assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trade_and_other_payables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_current_liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_noncurrent_liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">net_investing_cash_flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">net_financing_cash_flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">net_change_in_cash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opening_cash_and_cash_equivalents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asx-mlx  /  Operating</t>
+    <t xml:space="preserve">Trade and other receivables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total current assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total noncurrent assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade and other payables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total current liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total noncurrent liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net investing cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net financing cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net change in cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening cash and cash equivalents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASX:MLX  /  Operating</t>
   </si>
   <si>
     <t xml:space="preserve">Horizon</t>
@@ -6838,9 +6839,6 @@
     <t xml:space="preserve">see case input units</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Operating Cost</t>
   </si>
   <si>
@@ -6871,7 +6869,7 @@
     <t xml:space="preserve">Illustrative cash excludes financing, dividends and debt maturities. This is a finite cash-flow schedule, not an integrated three-statement forecast. No terminal perpetuity is assumed.</t>
   </si>
   <si>
-    <t xml:space="preserve">asx-mlx  /  Valuation</t>
+    <t xml:space="preserve">ASX:MLX  /  Valuation</t>
   </si>
   <si>
     <t xml:space="preserve">Enterprise Value</t>
@@ -6895,7 +6893,7 @@
     <t xml:space="preserve">This is a model output, not a price target or investment recommendation. Corporate costs and residual value are company-attributable; operating cash flows apply ownership once. Residual value is explicit, not a perpetuity.</t>
   </si>
   <si>
-    <t xml:space="preserve">asx-mlx  /  Sensitivities</t>
+    <t xml:space="preserve">ASX:MLX  /  Sensitivities</t>
   </si>
   <si>
     <t xml:space="preserve">Price multiplier × discount rate / AUD per share. All active-case forecast years recomputed, including positive-EBIT tax floor.</t>
@@ -6931,7 +6929,7 @@
     <t xml:space="preserve">Driver 1.2× / rate column 3</t>
   </si>
   <si>
-    <t xml:space="preserve">asx-mlx  /  Checks</t>
+    <t xml:space="preserve">ASX:MLX  /  Checks</t>
   </si>
   <si>
     <t xml:space="preserve">Valid active scenario</t>
@@ -6955,10 +6953,10 @@
     <t xml:space="preserve">Workbook checks are structural, not evidence approval. Import validates all scenarios, declared units, formula integrity and financial constraints independently. Any formula changes require a new model design review.</t>
   </si>
   <si>
-    <t xml:space="preserve">asx-mlx  /  Readme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WORKFLOW | Read the Markdown memo first. Excel is the editable detailed model. Change blue assumptions, recalculate, save and import to create a new validated research snapshot. Existing snapshots remain immutable.</t>
+    <t xml:space="preserve">ASX:MLX  /  Readme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">START HERE | Read the investment report first. Explore the detailed figures here. After changing blue assumptions, ask Codex to check the calculations and update the report. Earlier editions are retained.</t>
   </si>
   <si>
     <t xml:space="preserve">MODEL | One active scenario drives all formulas. Select bear/base/bull in Assumptions!B4. Forecast horizons are fixed by the source model; shorter cases have zero inputs after their final period.</t>
@@ -6973,7 +6971,7 @@
     <t xml:space="preserve">METHOD | Annual end-period discounting; explicit residual only. Positive EBIT tax floor; no deferred tax or loss carryforwards. Cash excludes debt repayment, funding and dividends. This is not an integrated income statement, balance sheet and cash-flow forecast.</t>
   </si>
   <si>
-    <t xml:space="preserve">EDITING | Blue inputs are editable. Green formulas link sheets. Black formulas calculate locally. Keep formulas and metadata intact. Synchronization records changed inputs as analyst overrides. Explain their source and rationale in the research memo; formula edits are rejected.</t>
+    <t xml:space="preserve">EDITING | Blue inputs are editable. Green formulas link sheets. Black formulas calculate locally. Change blue assumptions only. Explain the evidence behind each change in the investment report, then ask Codex to validate and save a new edition.</t>
   </si>
   <si>
     <t xml:space="preserve">EVIDENCE | A professional workbook layout does not upgrade uncertain evidence. Missing current quotes, mine-life support, payable sales or capital structure remain research gaps. Model values are not recommendations.</t>
@@ -7024,22 +7022,22 @@
     <t xml:space="preserve">investing-excel-v1</t>
   </si>
   <si>
-    <t xml:space="preserve">{"schema_version":1,"baseline":{"company_id":"asx-mlx","model_type":"finite_mine","purpose":"illustrative_sensitivity","synthetic":false,"currency":"AUD","valuation_date":"2026-09-20","reference_price":null,"quote_date":null,"cash":374000000.0,"debt":3285000.0,"other_assets":0.0,"diluted_shares":886391538.0,"historical":[{"entity":"Metals X Group","metric":"cash_and_cash_equivalents","value":293606000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"current_interest_bearing_liabilities","value":2849000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"noncurrent_interest_bearing_liabilities","value":436000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Limited","metric":"issued_ordinary_shares","value":886391538.0,"unit":"shares","currency":null,"period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=62","page":"62","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"rehabilitation_provision_present_value","value":33035000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=60","page":"60","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_operating_cash_flow","value":128323000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_paid_property_plant_equipment","value":13747000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_paid_mine_properties_development","value":22211000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Renison Tin Operation","metric":"tin_in_concentrate_produced","value":10748.0,"unit":"tonnes_tin","currency":null,"period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=9","page":"9","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"ownership_interest","value":0.5,"unit":"fraction","currency":null,"period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"tin_in_concentrate_produced","value":2809.0,"unit":"tonnes_tin","currency":null,"period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"tin_in_concentrate_produced","value":11287.0,"unit":"tonnes_tin","currency":null,"period":"TTM-ended-2026-06-30","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"imputed_tin_price","value":73834.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"imputed_tin_price","value":63760.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"TTM-ended-2026-06-30","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"c1_cash_production_cost","value":20251.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"c1_cash_production_cost","value":19349.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"TTM-ended-2026-06-30","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"imputed_sales_and_marketing_cost","value":8758.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"all_in_sustaining_cost","value":34865.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"capital_expenditure","value":23400000.0,"unit":"AUD","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","page":"3","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"sustaining_capital_expenditure","value":16450000.0,"unit":"AUD","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","page":"3","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"project_capital_expenditure","value":6950000.0,"unit":"AUD","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","page":"3","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Metals X Group","metric":"cash_and_cash_equivalents","value":374000000.0,"unit":"AUD","currency":"AUD","period":"2026-06-30","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=9","page":"9","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"corporate_costs","value":560000.0,"unit":"AUD","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","page":"8","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"revenue","value":284999000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"revenue","value":218820000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cost_of_sales","value":158275000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cost_of_sales","value":123558000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"gross_profit","value":126724000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"gross_profit","value":95262000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"general_and_administrative_expenses","value":4212000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"general_and_administrative_expenses","value":2744000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"finance_costs","value":980000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"finance_costs","value":566000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"profit_before_tax","value":138275000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"profit_before_tax","value":120227000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"income_tax_expense","value":33670000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"income_tax_expense","value":17878000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_income","value":104605000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_income","value":102349000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_and_cash_equivalents","value":220644000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"trade_and_other_receivables","value":36473000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"trade_and_other_receivables","value":8666000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"inventories","value":29488000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"inventories","value":37573000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_current_assets","value":363459000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_current_assets","value":271243000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_noncurrent_assets","value":255050000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_noncurrent_assets","value":233789000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_assets","value":618509000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_assets","value":505032000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"trade_and_other_payables","value":17091000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"trade_and_other_payables","value":20972000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"current_interest_bearing_liabilities","value":3645000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"noncurrent_interest_bearing_liabilities","value":2508000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_current_liabilities","value":51679000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_current_liabilities","value":43857000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_noncurrent_liabilities","value":34297000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_noncurrent_liabilities","value":33401000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_liabilities","value":85976000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_liabilities","value":77258000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_equity","value":532533000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_equity","value":427774000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_operating_cash_flow","value":143567000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_paid_property_plant_equipment","value":17425000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_paid_mine_properties_development","value":22511000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_investing_cash_flow","value":-52493000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_investing_cash_flow","value":-55453000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_financing_cash_flow","value":-2868000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_financing_cash_flow","value":-10512000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_change_in_cash","value":72962000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_change_in_cash","value":77602000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"opening_cash_and_cash_equivalents","value":220644000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"opening_cash_and_cash_equivalents","value":143042000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"}],"scenarios":{"bear":{"discount_rate":0.12,"ownership":0.5,"ownership_basis":"whole_operation","volume_basis":"imputed_production","residual_value":0.0,"years":[{"year":2027,"payable_tonnes":10158.3,"price":51008.0,"price_currency":"AUD","fx":1.0,"unit_cost":30181.8,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2028,"payable_tonnes":10158.3,"price":51008.0,"price_currency":"AUD","fx":1.0,"unit_cost":30181.8,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2029,"payable_tonnes":10158.3,"price":51008.0,"price_currency":"AUD","fx":1.0,"unit_cost":30181.8,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":100000000.0,"corporate_cost":2240000.0}],"notes":"Illustrative 3-year assumed finite horizon; not reserve-backed life. Price multiplier 0.8, unit-cost multiplier 1.1, production proxy multiplier 0.9; not guidance."},"base":{"discount_rate":0.1,"ownership":0.5,"ownership_basis":"whole_operation","volume_basis":"imputed_production","residual_value":0.0,"years":[{"year":2027,"payable_tonnes":11287.0,"price":63760.0,"price_currency":"AUD","fx":1.0,"unit_cost":27438.0,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2028,"payable_tonnes":11287.0,"price":63760.0,"price_currency":"AUD","fx":1.0,"unit_cost":27438.0,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2029,"payable_tonnes":11287.0,"price":63760.0,"price_currency":"AUD","fx":1.0,"unit_cost":27438.0,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2030,"payable_tonnes":11287.0,"price":63760.0,"price_currency":"AUD","fx":1.0,"unit_cost":27438.0,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2031,"payable_tonnes":11287.0,"price":63760.0,"price_currency":"AUD","fx":1.0,"unit_cost":27438.0,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":100000000.0,"corporate_cost":2240000.0}],"notes":"Illustrative 5-year assumed finite horizon; not reserve-backed life. Price multiplier 1.0, unit-cost multiplier 1.0, production proxy multiplier 1.0; not guidance."},"bull":{"discount_rate":0.08,"ownership":0.5,"ownership_basis":"whole_operation","volume_basis":"imputed_production","residual_value":0.0,"years":[{"year":2027,"payable_tonnes":12415.7,"price":76512.0,"price_currency":"AUD","fx":1.0,"unit_cost":26066.1,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2028,"payable_tonnes":12415.7,"price":76512.0,"price_currency":"AUD","fx":1.0,"unit_cost":26066.1,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2029,"payable_tonnes":12415.7,"price":76512.0,"price_currency":"AUD","fx":1.0,"unit_cost":26066.1,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2030,"payable_tonnes":12415.7,"price":76512.0,"price_currency":"AUD","fx":1.0,"unit_cost":26066.1,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2031,"payable_tonnes":12415.7,"price":76512.0,"price_currency":"AUD","fx":1.0,"unit_cost":26066.1,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2032,"payable_tonnes":12415.7,"price":76512.0,"price_currency":"AUD","fx":1.0,"unit_cost":26066.1,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":0.0,"corporate_cost":2240000.0},{"year":2033,"payable_tonnes":12415.7,"price":76512.0,"price_currency":"AUD","fx":1.0,"unit_cost":26066.1,"royalty_rate":0.0,"tax_rate":0.3,"depreciation":0.0,"capex":93600000.0,"working_capital_change":0.0,"closure":100000000.0,"corporate_cost":2240000.0}],"notes":"I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">llustrative 7-year assumed finite horizon; not reserve-backed life. Price multiplier 1.2, unit-cost multiplier 0.95, production proxy multiplier 1.1; not guidance."}},"provenance":{"/cash":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=9","rationale":"Reported group closing cash June 30 2026; no ownership scaling; stale at valuation date.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/debt":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","rationale":"Sum current 2,849,000 and noncurrent 436,000 financing liabilities at Dec 31 2025; stale proxy, not a verified current bridge.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/other_assets":{"unit":"AUD","source":"analyst-assumption://limited-sensitivity","rationale":"Exclude other investments/residual assets from this limited model; not a statement of zero economic value.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/diluted_shares":{"unit":"shares","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=62","rationale":"Issued-share denominator Dec 31 2025, NOT verified current diluted shares; illustrative only.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/discount_rate":{"unit":"fraction","source":"analyst-assumption://discount-rate","rationale":"Illustrative discount rate; not a derived company WACC.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/ownership":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"Reported 50% ownership of Renison; apply once to whole-operation FCF.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/residual_value":{"unit":"AUD","source":"analyst-assumption://finite-horizon","rationale":"No terminal perpetuity or residual asset value; horizon is an unverified stress assumption.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×0.9; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×0.8; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.1; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×0.9; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×0.8; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.1; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×0.9; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×0.8; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.1; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/discount_rate":{"unit":"fraction","source":"analyst-assumption://discount-rate","rationale":"Illustrative discount rate; not a derived company WACC.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/ownership":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"Reported 50% ownership of Renison; apply once to whole-operation FCF.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/residual_value":{"unit":"AUD","source":"analyst-assumption://finite-horizon","rationale":"No terminal perpetuity or residual asset value; horizon is an unverified stress assumption.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"},"/scenarios/base/years/3/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/discount_rate":{"unit":"fraction","source":"analyst-assumption://discount-rate","rationale":"Illustrative discount rate; not a derived company WACC.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/ownership":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"Reported 50% ownership of Renison; apply once to whole-operation FCF.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/residual_value":{"unit":"AUD","source":"analyst-assumption://finite-horizon","rationale":"No terminal perpetuity or residual asset value; horizon is an unverified stress assumption.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"}},"known_limitations":["ILLUSTRATIVE IMPUTED-REVENUE SENSITIVITY ONLY. This is not an actionable fair-value estimate or an investment recommendation.","Production is used solely as the company-style imputed-revenue proxy (100% produced tin sold/paid); it is NOT reported payable sales. The workbook labels it production_tonnes_proxy. Realized payable sales, inventory, settlement timing and revenue must replace this proxy before valuation.","The baseline price AUD63,760/t is the reported trailing-12-month LME-imputed price, NOT realized tin sales price. Scenario price and volume levels are analyst stress assumptions, not company guidance.","Unit cost combines reported trailing-12-month C1 AUD19,349/t and imputed sales/marketing AUD8,089/t. Marketing includes royalties and payable-tin deductions, so separate royalty_rate=0 prevents duplicate deductions. Price-linked marketing behavior is not separately modelled and could materially affect sensitivity.","Finite horizons 3/5/7 years are illustrative assumptions, not reserve-supported mine life. The quarterly report said an updated life-of-mine plan and Ore Reserve were expected in Q3 2026; those updates have not been verified. No perpetuity or residual value is included.","Cash AUD374m is as at June 30 2026; debt AUD3.285m and issued shares886,391,538 are as at December31 2025. These stale mixed-date balances need updated half-year/ASX checks. Issued shares are a proxy, NOT a verified current fully diluted denominator.","Closure is an explicit assumed AUD100m whole-operation nominal final-year payment. The reported AUD33.035m group rehabilitation provision is a present-value accounting figure, not this cash-payment estimate; actual scope/timing and other closure sites remain unmodelled.","Capex annualizes June-quarter whole-operation AUD23.4m to AUD93.6m each model year, including both sustaining and project spend. This is a scenario assumption, not guidance. No additional AISC deduction is made.","Annual corporate costs annualize group June-quarter AUD0.56m to AUD2.24m, deducted once after 50% attribution. Other investments/residual assets are set to zero only to exclude them from this limited sensitivity, not because they have zero economic value.","Tax rate30% is an analyst simplifying assumption; depreciation is assumed zero and no loss carryforwards, corporate tax shields or closure deductions are modelled. No forecast working-capital changes are assumed; this is not verified operational guidance.","Annual row labels2027 onward denote period-end annualized flows one/two/etc years from the valuation date, not an audited fiscal calendar projection. No remaining2026 stub cash flow is forecast. Forecast years are constant run-rate proxies.","No verified current share quote is supplied. Reverse valuation and price/upside comparisons are unavailable. No actual user portfolio is used.","Historical statement summaries now include FY2025 and FY2024 as reported in the 2025 annual report. This is a selected comparative history, not a full three-year normalization or a linked three-statement forecast. Group consolidated actuals must not be compared directly with unscaled whole-operation model rows."],"notes":"Public worked example. Reported historical figures are transcribed from issuer documents; future inputs are agent-authored illustrative assumptions, not management guidance. See MLX-MODEL-NOTES.md for source-page mapping, sign conventions and reconciliation checks."},"inputs":{"/cash":{"sheet":"Assumptions","cell":"B7"},"/debt":{"sheet":"Assumptions","cell":"B8"},"/other_assets":{"sheet":"Assumptions","cell":"B9"},"/diluted_shares":{"sheet":"Assumptions","cell":"B10"},"/reference_price":{"sheet":"Assumptions","cell":"B11"},"/valuation_date":{"sheet":"Assumptions","cell":"B12"},"/quote_date":{"sheet":"Assumptions","cell":"B13"},"/scenarios/bear/discount_rate":{"sheet":"Assumptions","cell":"B20"},"/scenarios/bear/ownership":{"sheet":"Assumptions","cell":"B21"},"/scenarios/bear/residual_value":{"sheet":"Assumptions","cell":"B22"},"/scenarios/bear/years/0/payable_tonnes":{"sheet":"Assumptions","cell":"C25"},"/scenarios/bear/years/1/payable_tonnes":{"sheet":"Assumptions","cell":"D25"},"/scenarios/bear/years/2/payable_tonnes":{"sheet":"Assumptions","cell":"E25"},"/scenarios/bear/years/0/price":{"sheet":"Assumptions","cell":"C26"},"/scenarios/bear/years/1/price":{"sheet":"Assumptions","cell":"D26"},"/scenarios/bear/years/2/price":{"sheet":"Assumptions","cell":"E26"},"/scenarios/bear/years/0/fx":{"sheet":"Assumptions","cell":"C27"},"/scenarios/bear/years/1/fx":{"sheet":"Assumptions","cell":"D27"},"/scenarios/bear/years/2/fx":{"sheet":"Assumptions","cell":"E27"},"/scenarios/bear/years/0/unit_cost":{"sheet":"Assumptions","cell":"C28"},"/scenarios/bear/years/1/unit_cost":{"sheet":"Assumptions","cell":"D28"},"/scenarios/bear/years/2/unit_cost":{"sheet":"Assumptions","cell":"E28"},"/scenarios/bear/years/0/royalty_rate":{"sheet":"Assumptions","cell":"C29"},"/scenarios/bear/years/1/royalty_rate":{"sheet":"Assumptions","cell":"D29"},"/scenarios/bear/years/2/royalty_rate":{"sheet":"Assumptions","cell":"E29"},"/scenarios/bear/years/0/tax_rate":{"sheet":"Assumptions","cell":"C30"},"/scenarios/bear/years/1/tax_rate":{"sheet":"Assumptions","cell":"D30"},"/scenarios/bear/years/2/tax_rate":{"sheet":"Assumptions","cell":"E30"},"/scenarios/bear/years/0/depreciation":{"sheet":"Assumptions","cell":"C31"},"/scenarios/bear/years/1/depreciation":{"sheet":"Assumptions","cell":"D31"},"/scenarios/bear/years/2/depreciation":{"sheet":"Assumptions","cell":"E31"},"/scenarios/bear/years/0/capex":{"sheet":"Assumptions","cell":"C32"},"/scenarios/bear/years/1/capex":{"sheet":"Assumptions","cell":"D32"},"/scenarios/bear/years/2/capex":{"sheet":"Assumptions","cell":"E32"},"/scenarios/bear/years/0/working_capital_change":{"sheet":"Assumptions","cell":"C33"},"/scenarios/bear/years/1/working_capital_change":{"sheet":"Assumptions","cell":"D33"},"/scenarios/bear/years/2/working_capital_change":{"sheet":"Assumptions","cell":"E33"},"/scenarios/bear/years/0/closure":{"sheet":"Assumptions","cell":"C34"},"/scenarios/bear/years/1/closure":{"sheet":"Assumptions","cell":"D34"},"/scenarios/bear/years/2/closure":{"sheet":"Assumptions","cell":"E34"},"/scenarios/bear/years/0/corporate_cost":{"sheet":"Assumptions","cell":"C35"},"/scenarios/bear/years/1/corporate_cost":{"sheet":"Assumptions","cell":"D35"},"/scenarios/bear/years/2/corporate_cost":{"sheet":"Assumptions","cell":"E35"},"/scenarios/base/discount_rate":{"sheet":"Assumptions","cell":"B39"},"/scenarios/base/ownership":{"sheet":"Assumptions","cell":"B40"},"/scenarios/base/residual_value":{"sheet":"Assumptions","cell":"B41"},"/scenarios/base/years/0/payable_tonnes":{"sheet":"Assumptions","cell":"C44"},"/scenarios/base/years/1/payable_tonnes":{"sheet":"Assumptions","cell":"D44"},"/scenarios/base/years/2/payable_tonnes":{"sheet":"Assumptions","cell":"E44"},"/scenarios/base/years/3/payable_tonnes":{"sheet":"Assumptions","cell":"F44"},"/scenarios/base/years/4/payable_tonnes":{"sheet":"Assumptions","cell":"G44"},"/scenarios/base/years/0/price":{"sheet":"Assumptions","cell":"C45"},"/scenarios/base/years/1/price":{"sheet":"Assumptions","cell":"D45"},"/scenarios/base/years/2/price":{"sheet":"Assumptions","cell":"E45"},"/scenarios/base/years/3/price":{"sheet":"Assumptions","cell":"F45"},"/scenarios/base/years/4/price":{"sheet":"Assumptions","cell":"G45"},"/scenarios/base/years/0/fx":{"sheet":"Assumptions","cell":"C46"},"/scenarios/base/years/1/fx":{"sheet":"Assumptions","cell":"D46"},"/scenarios/base/years/2/fx":{"sheet":"Assumptions","cell":"E46"},"/scenarios/base/years/3/fx":{"sheet":"Assumptions","cell":"F46"},"/scenarios/base/years/4/fx":{"sheet":"Assumptions","cell":"G46"},"/scenarios/base/years/0/unit_cost":{"sheet":"Assumptions","cell":"C47"},"/scenarios/base/years/1/unit_cost":{"sheet":"Assumptions","cell":"D47"},"/scenarios/base/years/2/unit_cost":{"sheet":"Assumptions","cell":"E47"},"/scenarios/base/years/3/unit_cost":{"sheet":"Assumptions","cell":"F47"},"/scenarios/base/years/4/unit_cost":{"sheet":"Assumptions","cell":"G47"},"/scenarios/base/years/0/royalty_rate":{"sheet":"Assumptions","cell":"C48"},"/scenarios/base/years/1/royalty_rate":{"sheet":"Assumptions","cell":"D48"},"/scenarios/base/years/2/royalty_rate":{"sheet":"Assumptions","cell":"E48"},"/scenarios/base/years/3/royalty_rate":{"sheet":"Assumptions","cell":"F48"},"/scenarios/base/years/4/royalty_rate":{"sheet":"Assumptions","cell":"G48"},"/scenarios/base/years/0/tax_rate":{"sheet":"Assumptions","cell":"C49"},"/scenarios/base/years/1/tax_rate":{"sheet":"Assumptions","cell":"D49"},"/scenarios/base/years/2/tax_rate":{"sheet":"Assumptions","cell":"E49"},"/scenarios/base/years/3/tax_rate":{"sheet":"Assumptions","cell":"F49"},"/scenarios/base/years/4/tax_rate":{"sheet":"Assumptions","cell":"G49"},"/scenarios/base/years/0/depreciation":{"sheet":"Assumptions","cell":"C50"},"/scenarios/base/years/1/depreciation":{"sheet":"Assumptions","cell":"D50"},"/scenarios/base/years/2/depreciation":{"sheet":"Assumptions","cell":"E50"},"/scenarios/base/years/3/depreciation":{"sheet":"Assumptions","cell":"F50"},"/scenarios/base/years/4/depreciation":{"sheet":"Assumptions","cell":"G50"},"/scenarios/base/years/0/capex":{"sheet":"Assumptions","cell":"C51"},"/scenarios/base/years/1/capex":{"sheet":"Assumptions","cell":"D51"},"/scenarios/base/years/2/capex":{"sheet":"Assumptions","cell":"E51"},"/scenarios/base/years/3/capex":{"sheet":"Assumptions","cell":"F51"},"/scenarios/base/years/4/capex":{"sheet":"Assumptions","cell":"G51"},"/scenarios/base/years/0/working_capital_change":{"sheet":"Assumptions","cell":"C52"},"/scenarios/base/years/1/working_capital_change":{"sheet":"Assumptions","cell":"D52"},"/scenarios/base/years/2/working_capital_change":{"sheet":"Assumptions","cell":"E52"},"/scenarios/base/years/3/working_capital_change":{"sheet":"Assumptions","cell":"F52"},"/scenarios/base/years/4/working_capital_change":{"sheet":"Assumptions","cell":"G52"},"/scenarios/base/years/0/closure":{"sheet":"Assumptions","cell":"C53"},"/scenarios/base/years/1/closure":{"sheet":"Assumptions","cell":"D53"},"/scenarios/base/years/2/closure":{"sheet":"Assumptions","cell":"E53"},"/scenarios/base/years/3/closure":{"sheet":"Assumptions","cell":"F53"},"/scenarios/base/years/4/closure":{"sheet":"Assumptions","cell":"G53"},"/scenarios/base/years/0/corporate_cost":{"sheet":"Assumptions","cell":"C54"},"/scenarios/base/years/1/corporate_cost":{"sheet":"Assumptions","cell":"D54"},"/scenarios/base/years/2/corporate_cost":{"sheet":"Assumptions","cell":"E54"},"/scenarios/base/years/3/corporate_cost":{"sheet":"Assumptions","cell":"F54"},"/scenarios/base/years/4/corporate_cost":{"sheet":"Assumptions","cell":"G54"},"/scenarios/bull/discount_rate":{"sheet":"Assumptions","cell":"B58"},"/scenarios/bull/ownership":{"sheet":"Assumptions","cell":"B59"},"/scenarios/bull/residual_value":{"sheet":"Assumptions","cell":"B60"},"/scenarios/bull/years/0/payable_tonnes":{"sheet":"Assumptions","cell":"C63"},"/scenarios/bull/years/1/payable_tonnes":{"sheet":"Assumptions","cell":"D63"},"/scenarios/bull/years/2/payable_tonnes":{"sheet":"Assumptions","cell":"E63"},"/scenarios/bull/years/3/payable_tonnes":{"sheet":"Assumptions","cell":"F63"},"/scenarios/bull/years/4/payable_tonnes":{"sheet":"Assumptions","cell":"G63"},"/scenarios/bull/years/5/payable_tonnes":{"sheet":"Assumptions","cell":"H63"},"/scenarios/bull/years/6/payable_tonnes":{"sheet":"Assumptions","cell":"I63"},"/scenarios/bull/years/0/price":{"sheet":"Assumptions","cell":"C64"},"/scenarios/bull/years/1/price":{"sheet":"Assumptions","cell":"D64"},"/scenarios/bull/years/2/price":{"sheet":"Assumptions","cell":"E64"},"/scenarios/bull/years/3/price":{"sheet":"Assumptions","cell":"F64"},"/scenarios/bull/years/4/price":{"sheet":"Assumptions","cell":"G64"},"/scenarios/bull/years/5/price":{"sheet":"Assumptions","cell":"H64"},"/scenarios/bull/years/6/price":{"sheet":"Assumptions","cell":"I64"},"/scenarios/bull/years/0/fx":{"sheet":"Assumptions","cell":"C65"},"/scenarios/bull/years/1/fx":{"sheet":"Assumptions","cell":"D65"},"/scenarios/bull/years/2/fx":{"sheet":"Assumptions","cell":"E65"},"/scenarios/bull/years/3/fx":{"sheet":"Assumptions","cell":"F65"},"/scenarios/bull/years/4/fx":{"sheet":"Assumptions","cell":"G65"},"/scenarios/bull/years/5/fx":{"sheet":"Assumptions","cell":"H65"},"/scenarios/bull/years/6/fx":{"sheet":"Assumptions","cell":"I65"},"/scenarios/bull/years/0/unit_cost":{"sheet":"Assumptions","cell":"C66"},"/scenarios/bull/years/1/unit_cost":{"sheet":"Assumptions","cell":"D66"},"/scenarios/bull/years/2/unit_cost":{"sheet":"Assumptions","cell":"E66"},"/scenarios/bull/years/3/unit_cost":{"sheet":"Assumptions","cell":"F66"},"/scenarios/bull/years/4/unit_cost":{"sheet":"Assumptions","cell":"G66"},"/scenarios/bull/years/5/unit_cost":{"sheet":"Assumptions","cell":"H66"},"/scenarios/bull/years/6/unit_cost":{"sheet":"Assumptions","cell":"I66"},"/scenarios/bull/years/0/royalty_rate":{"sheet":"Assumptions","cell":"C67"},"/scenarios/bull/years/1/royalty_rate":{"sheet":"Assumptions","cell":"D67"},"/scenarios/bull/years/2/royalty_rate":{"sheet":"Assumptions","cell":"E67"},"/scenarios/bull/years/3/royalty_rate":{"sheet":"Assumptions","cell":"F67"},"/scenarios/bull/years/4/royalty_rate":{"sheet":"Assumptions","cell":"G67"},"/scenarios/bull/years/5/royalty_rate":{"sheet":"Assumptions","cell":"H67"},"/scenarios/bull/years/6/royalty_rate":{"sheet":"Assumptions","cell":"I67"},"/scenarios/bull/years/0/tax_rate":{"sheet":"Assumptions","cell":"C68"},"/scenarios/bull/years/1/tax_rate":{"sheet":"Assumptions","cell":"D68"},"/scenarios/bull/years/2/tax_rate":{"sheet":"Assumptions","cell":"E68"},"/scenarios/bull/years/3/tax_rate":{"sheet":"Assumptions","cell":"F68"},"/scenarios/bull/years/4/tax_rate":{"sheet":"Assumptions","cell":"G68"},"/scenarios/bull/years/5/tax_rate":{"sheet":"Assumptions","cell":"H68"},"/scenarios/bull/years/6/tax_rate":{"sheet":"Assumptions","cell":"I68"},"/scenarios/bull/years/0/depreciation":{"sheet":"Assumptions","cell":"C69"},"/scenarios/bull/years/1/depreciation":{"sheet":"Assumptions","cell":"D69"},"/scenarios/bull/years/2/depreciation":{"sheet":"Assumptions","cell":"E69"},"/scenarios/bull/years/3/depreciation":{"sheet":"Assumptions","cell":"F69"},"/scenarios/bull/years/4/depreciation":{"sheet":"Assumptions","cell":"G69"},"/scenarios/bull/years/5/depreciation":{"sheet":"Assumptions","cell":"H69"},"/scenarios/bull/years/6/depreciation":{"sheet":"Assumptions","cell":"I69"},"/scenarios/bull/years/0/capex":{"sheet":"Assumptions","cell":"C70"},"/scenarios/bull/years/1/capex":{"sheet":"Assumptions","cell":"D70"},"/scenarios/bull/years/2/capex":{"sheet":"Assumptions","cell":"E70"},"/scenarios/bull/years/3/capex":{"sheet":"Assumptions","cell":"F70"},"/scenarios/bull/years/4/capex":{"sheet":"Assumptions","cell":"G70"},"/scenarios/bull/years/5/capex":{"sheet":"Assumptions","cell":"H70"},"/scenarios/bull/years/6/capex":{"sheet":"Assumptions","cell":"I70"},"/scenarios/bull/years/0/working_capital_change":{"sheet":"Assumptions","cell":"C71"},"/scenarios/bull/years/1/working_capital_change":{"sheet":"Assumptions","cell":"D71"},"/scenarios/bull/years/2/working_capital_change":{"sheet":"Assumptions","cell":"E71"},"/scenarios/bull/years/3/working_capital_change":{"sheet":"Assumptions","cell":"F71"},"/scenarios/bull/years/4/working_capital_change":{"sheet":"Assumptions","cell":"G71"},"/scenarios/bull/years/5/working_capital_change":{"sheet":"Assumptions","cell":"H71"},"/scenarios/bull/years/6/working_capital_change":{"sheet":"Assumptions","cell":"I71"},"/scenarios/bull/years/0/closure":{"sheet":"Assumptions","cell":"C72"},"/scenarios/bull/years/1/closure":{"sheet":"Assumptions","cell":"D72"},"/scenarios/bull/years/2/closure":{"sheet":"Assumptions","cell":"E72"},"/scenarios/bull/years/3/closure":{"sheet":"Assumptions","cell":"F72"},"/scenarios/bull/years/4/closure":{"sheet":"Assumptions","cell":"G72"},"/scenarios/bull/years/5/closure":{"sheet":"Assumptions","cell":"H72"},"/scenarios/bull/years/6/closure":{"sheet":"Assumptions","cell":"I72"},"/scenarios/bull/years/0/corporate_cost":{"sheet":"Assumptions","cell":"C73"},"/scenarios/bull/years/1/corporate_cost":{"sheet":"Assumptions","cell":"D73"},"/scenarios/bull/years/2/corporate_cost":{"sheet":"Assumptions","cell":"E73"},"/scenarios/bull/years/3/corporate_cost":{"sheet":"Assumptions","cell":"F73"},"/scenarios/bull/years/4/corporate_cost":{"sheet":"Assumptions","cell":"G73"},"/scenarios/bull/years/5/corporate_cost":{"sheet":"Assumptions","cell":"H73"},"/scenarios/bull/years/6/corporate_cost":{"sheet":"Assumptions","cell":"I73"}},"outputs":{"active_case":{"sheet":"Assumptions","cell":"B4"},"years/0/year":{"sheet":"Operating","cell":"C9"},"years/0/revenue":{"sheet":"Operating","cell":"C23"},"years/0/operating_cost":{"sheet":"Operating","cell":"C24"},"years/0/royalties":{"sheet":"Operating","cell":"C25"},"years/0/ebit":{"sheet":"Operating","cell":"C26"},"years/0/tax":{"sheet":"Operating","cell":"C27"},"years/0/nopat":{"sheet":"Operating","cell":"C28"},"years/0/operating_fcf":{"sheet":"Operating","cell":"C29"},"years/0/fcf":{"sheet":"Operating","cell":"C30"},"years/0/present_value":{"sheet":"Operating","cell":"C31"},"years/0/illustrative_cash":{"sheet":"Operating","cell":"C32"},"years/1/year":{"sheet":"Operating","cell":"D9"},"years/1/revenue":{"sheet":"Operating","cell":"D23"},"years/1/operating_cost":{"sheet":"Operating","cell":"D24"},"years/1/royalties":{"sheet":"Operating","cell":"D25"},"years/1/ebit":{"sheet":"Operating","cell":"D26"},"years/1/tax":{"sheet":"Operating","cell":"D27"},"years/1/nopat":{"sheet":"Operating","cell":"D28"},"years/1/operating_fcf":{"sheet":"Operating","cell":"D29"},"years/1/fcf":{"sheet":"Operating","cell":"D30"},"years/1/present_value":{"sheet":"Operating","cell":"D31"},"years/1/illustrative_cash":{"sheet":"Operating","cell":"D32"},"years/2/year":{"sheet":"Operating","cell":"E9"},"years/2/revenue":{"sheet":"Operating","cell":"E23"},"years/2/operating_cost":{"sheet":"Operating","cell":"E24"},"years/2/royalties":{"sheet":"Operating","cell":"E25"},"years/2/ebit":{"sheet":"Operating","cell":"E26"},"years/2/tax":{"sheet":"Operating","cell":"E27"},"years/2/nopat":{"sheet":"Operating","cell":"E28"},"years/2/operating_fcf":{"sheet":"Operating","cell":"E29"},"years/2/fcf":{"sheet":"Operating","cell":"E30"},"years/2/present_value":{"sheet":"Operating","cell":"E31"},"years/2/illustrative_cash":{"sheet":"Operating","cell":"E32"},"years/3/year":{"sheet":"Operating","cell":"F9"},"years/3/revenue":{"sheet":"Operating","cell":"F23"},"years/3/operating_cost":{"sheet":"Operating","cell":"F24"},"years/3/royalties":{"sheet":"Operating","cell":"F25"},"years/3/ebit":{"sheet":"Operating","cell":"F26"},"years/3/tax":{"sheet":"Operating","cell":"F27"},"years/3/nopat":{"sheet":"Operating","cell":"F28"},"years/3/operating_fcf":{"sheet":"Operating","cell":"F29"},"years/3/fcf":{"sheet":"Operating","cell":"F30"},"years/3/present_value":{"sheet":"Operating","cell":"F31"},"years/3/illustrative_cash":{"sheet":"Operating","cell":"F32"},"years/4/year":{"sheet":"Operating","cell":"G9"},"years/4/revenue":{"sheet":"Operating","cell":"G23"},"years/4/operating_cost":{"sheet":"Operating","cell":"G24"},"years/4/royalties":{"sheet":"Operating","cell":"G25"},"years/4/ebit":{"sheet":"Operating","cell":"G26"},"years/4/tax":{"sheet":"Operating","cell":"G27"},"years/4/nopat":{"sheet":"Operating","cell":"G28"},"years/4/operating_fcf":{"sheet":"Operating","cell":"G29"},"years/4/fcf":{"sheet":"Operating","cell":"G30"},"years/4/present_value":{"sheet":"Operating","cell":"G31"},"years/4/illustrative_cash":{"sheet":"Operating","cell":"G32"},"years/5/year":{"sheet":"Operating","cell":"H9"},"years/5/revenue":{"sheet":"Operating","cell":"H23"},"years/5/operating_cost":{"sheet":"Operating","cell":"H24"},"years/5/royalties":{"sheet":"Operating","cell":"H25"},"years/5/ebit":{"sheet":"Operating","cell":"H26"},"years/5/tax":{"sheet":"Operating","cell":"H27"},"years/5/nopat":{"sheet":"Operating","cell":"H28"},"years/5/operating_fcf":{"sheet":"Operating","cell":"H29"},"years/5/fcf":{"sheet":"Operating","cell":"H30"},"years/5/present_value":{"sheet":"Operating","cell":"H31"},"years/5/illustrative_cash":{"sheet":"Operating","cell":"H32"},"years/6/year":{"sheet":"Operating","cell":"I9"},"years/6/revenue":{"sheet":"Operating","cell":"I23"},"years/6/operating_cost":{"sheet":"Operating","cell":"I24"},"years/6/royalties":{"sheet":"Operating","cell":"I25"},"years/6/ebit":{"sheet":"Operating","cell":"I26"},"years/6/tax":{"sheet":"Operating","cell":"I27"},"years/6/nopat":{"sheet":"Operating","cell":"I28"},"years/6/operating_fcf":{"sheet":"Operating","cell":"I29"},"years/6/fcf":{"sheet":"Operating","cell":"I30"},"years/6/present_value":{"sheet":"Operating","cell":"I31"},"years/6/illustrative_cash":{"sheet":"Operating","cell":"I32"},"enterprise_value":{"sheet":"Valuation","cell":"B5"},"cash":{"sheet":"Valuation","cell":"B6"},"other_assets":{"sheet":"Valuation","cell":"B7"},"debt":{"sheet":"Valuation","cell":"B8"},"equity_value":{"sheet":"Valuation","cell":"B9"},"diluted_shares":{"sheet":"Valuation","cell":"B10"},"per_share":{"sheet":"Valuation","cell":"B11"},"minimum_illustrative_cash":{"sheet":"Valuation","cell":"B12"},"discount_rate/0":{"sheet":"Sensitivities","cell":"C7"},"discount_rate/1":{"sheet":"Sensitivities","cell":"D7"},"discount_rate/2":{"sheet":"Sensitivities","cell":"E7"},"driver_multiplier/0":{"sheet":"Sensitivities","cell":"B8"},"sensitivity/0/0":{"sheet":"Sensitivities","cell":"C8"},"sensitivity/0/1":{"sheet":"Sensitivities","cell":"D8"},"sensitivity/0/2":{"sheet":"Sensitivities","cell":"E8"},"driver_multiplier/1":{"sheet":"Sensitivities","cell":"B9"},"sensitivity/1/0":{"sheet":"Sensitivities","cell":"C9"},"sensitivity/1/1":{"sheet":"Sensitivities","cell":"D9"},"sensitivity/1/2":{"sheet":"Sensitivities","cell":"E9"},"driver_multiplier/2":{"sheet":"Sensitivities","cell":"B10"},"sensitivity/2/0":{"sheet":"Sensitivities","cell":"C10"},"sensitivity/2/1":{"sheet":"Sensitivities","cell":"D10"},"sensitivity/2/2":{"sheet":"Sensitivities","cell":"E10"},"checks/0":{"sheet":"Checks","cell":"B5"},"checks/1":{"sheet":"Checks","cell":"B6"},"checks/2":{"sheet":"Checks","cell":"B7"},"checks/3":{"sheet":"Checks","cell":"B8"},"checks/4":{"sheet":"Checks","cell":"B9"},"checks/5":{"sheet":"Checks","cell":"B10"}},"formula_cells":{"Operating!B4":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$B$20,IF(Assumptions!$B$4=\"base\",'Assumptions'!$B$39,'Assumptions'!$B$58))","Operating!B5":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$B$21,IF(Assumptions!$B$4=\"base\",'Assumptions'!$B$40,'Assumptions'!$B$59))","Operating!B6":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$B$22,IF(Assumptions!$B$4=\"base\",'Assumptions'!$B$41,'Assumptions'!$B$60))","Operating!B7":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$B$23,IF(Assumptions!$B$4=\"base\",'Assumptions'!$B$42,'Assumptions'!$B$61))","Operating!B8":"=IF(Assumptions!$B$4=\"bear\",\"imputed_production\",IF(Assumptions!$B$4=\"base\",\"imputed_production\",\"imputed_production\"))","Operating!C9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+1","Operating!C10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$44,'Assumptions'!$C$63))","Operating!C11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$45,'Assumptions'!$C$64))","Operating!C12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$46,'Assumptions'!$C$65))","Operating!C13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$47,'Assumptions'!$C$66))","Operating!C14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$48,'Assumptions'!$C$67))","Operating!C15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$49,'Assumptions'!$C$68))","Operating!C16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$50,'Assumptions'!$C$69))","Operating!C17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$51,'Assumptions'!$C$70))","Operating!C18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$52,'Assumptions'!$C$71))","Operating!C19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$53,'Assumptions'!$C$72))","Operating!C20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$54,'Assumptions'!$C$73))","Operating!C23":"='Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12","Operating!C24":"='Operating'!$C$10*'Operating'!$C$13","Operating!C25":"='Operating'!$C$23*'Operating'!$C$14","Operating!C26":"='Operating'!$C$23-'Operating'!$C$24-'Operating'!$C$25-'Operating'!$C$16","Operating!C27":"=MAX(0,'Operating'!$C$26)*'Operating'!$C$15","Operating!C28":"='Operating'!$C$26-'Operating'!$C$27","Operating!C29":"='Operating'!$C$28+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19","Operating!C30":"='Operating'!$C$29*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0)","Operating!C31":"='Operating'!$C$30/(1+'Operating'!$B$4)^1","Operating!C32":"='Assumptions'!$B$7+'Operating'!$C$30","Operating!D9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+2","Operating!D10":"=IF(Assumpt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ions!$B$4=\"bear\",'Assumptions'!$D$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$44,'Assumptions'!$D$63))","Operating!D11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$45,'Assumptions'!$D$64))","Operating!D12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$46,'Assumptions'!$D$65))","Operating!D13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$47,'Assumptions'!$D$66))","Operating!D14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$48,'Assumptions'!$D$67))","Operating!D15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$49,'Assumptions'!$D$68))","Operating!D16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$50,'Assumptions'!$D$69))","Operating!D17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$51,'Assumptions'!$D$70))","Operating!D18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$52,'Assumptions'!$D$71))","Operating!D19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$53,'Assumptions'!$D$72))","Operating!D20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$54,'Assumptions'!$D$73))","Operating!D23":"='Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12","Operating!D24":"='Operating'!$D$10*'Operating'!$D$13","Operating!D25":"='Operating'!$D$23*'Operating'!$D$14","Operating!D26":"='Operating'!$D$23-'Operating'!$D$24-'Operating'!$D$25-'Operating'!$D$16","Operating!D27":"=MAX(0,'Operating'!$D$26)*'Operating'!$D$15","Operating!D28":"='Operating'!$D$26-'Operating'!$D$27","Operating!D29":"='Operating'!$D$28+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19","Operating!D30":"='Operating'!$D$29*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0)","Operating!D31":"='Operating'!$D$30/(1+'Operating'!$B$4)^2","Operating!D32":"='Operating'!$C$32+'Operating'!$D$30","Operating!E9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+3","Operating!E10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$44,'Assumptions'!$E$63))","Operating!E11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$45,'Assumptions'!$E$64))","Operating!E12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$46,'Assumptions'!$E$65))","Operating!E13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$47,'Assumptions'!$E$66))","Operating!E14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$48,'Assumptions'!$E$67))","Operating!E15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$49,'Assumptions'!$E$68))","Operating!E16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$50,'Assumptions'!$E$69))","Operating!E17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$51,'Assumptions'!$E$70))","Operating!E18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$52,'Assumptions'!$E$71))","Operating!E19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$53,'Assumptions'!$E$72))","Operating!E20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$54,'Assumptions'!$E$73))","Operating!E23":"='Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12","Operating!E24":"='Operating'!$E$10*'Operating'!$E$13","Operating!E25":"='Operating'!$E$23*'Operating'!$E$14","Operating!E26":"='Operating'!$E$23-'Operating'!$E$24-'Operating'!$E$25-'Operating'!$E$16","Operating!E27":"=MAX(0,'Operating'!$E$26)*'Operating'!$E$15","Operating!E28":"='Operating'!$E$26-'Operating'!$E$27","Operating!E29":"='Operating'!$E$28+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19","Operating!E30":"='Operating'!$E$29*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0)","Operating!E31":"='Operating'!$E$30/(1+'Operating'!$B$4)^3","Operating!E32":"='Operating'!$D$32+'Operating'!$E$30","Operating!F9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+4","Operating!F10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$44,'Assumptions'!$F$63))","Operating!F11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$45,'Assumptions'!$F$64))","Operating!F12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$46,'Assumptions'!$F$65))","Operating!F13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$47,'Assumptions'!$F$66))","Operating!F14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$48,'Assumptions'!$F$67))","Operating!F15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$49,'Assumptions'!$F$68))","Operating!F16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$50,'Assumptions'!$F$69))","Operating!F17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$51,'Assumptions'!$F$70))","Operating!F18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$52,'Assumptions'!$F$71))","Operating!F19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$53,'Assumptions'!$F$72))","Operating!F20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$54,'Assumptions'!$F$73))","Operating!F23":"='Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12","Operating!F24":"='Operating'!$F$10*'Operating'!$F$13","Operating!F25":"='Operating'!$F$23*'Operating'!$F$14","Operating!F26":"='Operating'!$F$23-'Operating'!$F$24-'Operating'!$F$25-'Operating'!$F$16","Operating!F27":"=MAX(0,'Operating'!$F$26)*'Operating'!$F$15","Operating!F28":"='Operating'!$F$26-'Operating'!$F$27","Operating!F29":"='Operating'!$F$28+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19","Operating!F30":"='Operating'!$F$29*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0)","Operating!F31":"='Operating'!$F$30/(1+'Operating'!$B$4)^4","Operating!F32":"='Operating'!$E$32+'Operating'!$F$30","Operating!G9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+5","Operating!G10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$44,'Assumptions'!$G$63))","Operating!G11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$45,'Assumptions'!$G$64))","Operating!G12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$46,'Assumptions'!$G$65))","Operating!G13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$47,'Assumptions'!$G$66))","Operating!G14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$48,'Assumptions'!$G$67))","Operating!G15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$49,'Assumptions'!$G$68))","Operating!G16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$50,'Assumptions'!$G$69))","Operating!G17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$51,'Assumptions'!$G$70))","Operating!G18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$52,'Assumptions'!$G$71))","Operating!G19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$53,'Assumptions'!$G$72))","Operating!G20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$54,'Assumptions'!$G$73))","Operating!G23":"='Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12","Operating!G24":"='Operating'!$G$10*'Operating'!$G$13","Operating!G25":"='Operating'!$G$23*'Operating'!$G$14","Operating!G26":"='Operating'!$G$23-'Operating'!$G$24-'Operating'!$G$25-'Operating'!$G$16","Operating!G27":"=MAX(0,'Operating'!$G$26)*'Operating'!$G$15","Operating!G28":"='Operating'!$G$26-'Operating'!$G$27","Operating!G29":"='Operating'!$G$28+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19","Operating!G30":"='Operating'!$G$29*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0)","Operating!G31":"='Operating'!$G$30/(1+'Operating'!$B$4)^5","Operating!G32":"='Operating'!$F$32+'Operating'!$G$30","Operating!H9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+6","Operating!H10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$44,'Assumptions'!$H$63))","Operating!H11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$45,'Assumptions'!$H$64))","Operating!H12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$46,'Assumptions'!$H$65))","Operating!H13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$47,'Assumptions'!$H$66))","Operating!H14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$48,'Assumptions'!$H$67))","Operating!H15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$49,'Assumptions'!$H$68))","Operating!H16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$50,'Assumptions'!$H$69))","Operating!H17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$51,'Assumptions'!$H$70))","Operating!H18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$52,'Assumptions'!$H$71))","Operating!H19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$53,'Assumptions'!$H$72))","Operating!H20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$54,'Assumptions'!$H$73))","Operating!H23":"='Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12","Operating!H24":"='Operating'!$H$10*'Operating'!$H$13","Operating!H25":"='Operating'!$H$23*'Operating'!$H$14","Operating!H26":"='Operating'!$H$23-'Operating'!$H$24-'Operating'!$H$25-'Operating'!$H$16","Operating!H27":"=MAX(0,'Operating'!$H$26)*'Operating'!$H$15","Operating!H28":"='Operating'!$H$26-'Operating'!$H$27","Operating!H29":"='Operating'!$H$28+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19","Operating!H30":"='Operating'!$H$29*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0)","Operating!H31":"='Operating'!$H$30/(1+'Operating'!$B$4)^6","Operating!H32":"='Operating'!$G$32+'Operating'!$H$30","Operating!I9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+7","Operating!I10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$44,'Assumptions'!$I$63))","Operating!I11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$45,'Assumptions'!$I$64))","Operating!I12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$46,'Assumptions'!$I$65))","Operating!I13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$47,'Assumptions'!$I$66))","Operating!I14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$48,'Assumptions'!$I$67))","Operating!I15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$49,'Assumptions'!$I$68))","Operating!I16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$50,'Assumptions'!$I$69))","Operating!I17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$51,'Assumptions'!$I$70))","Operating!I18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$52,'Assumptions'!$I$71))","Operating!I19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$53,'Assumptions'!$I$72))","Operating!I20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$54,'Assumptions'!$I$73))","Operating!I23":"='Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12","Operating!I24":"='Operating'!$I$10*'Operating'!$I$13","Operating!I25":"='Operating'!$I$23*'Operating'!$I$14","Operating!I26":"='Operating'!$I$23-'Operating'!$I$24-'Operating'!$I$25-'Operating'!$I$16","Operating!I27":"=MAX(0,'Operating'!$I$26)*'Operating'!$I$15","Operating!I28":"='Operating'!$I$26-'Operating'!$I$27","Operating!I29":"='Operating'!$I$28+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19","Operating!I30":"='Operating'!$I$29*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0)","Operating!I31":"='Operating'!$I$30/(1+'Operating'!$B$4)^7","Operating!I32":"='Operating'!$H$32+'Operating'!$I$30","Valuation!B5":"=SUM(Operating!C31:I31)","Valuation!B6":"='Assumptions'!$B$7","Valuation!B7":"='Assumptions'!$B$9","Valuation!B8":"='Assumptions'!$B$8","Valuation!B9":"=B5+B6+B7-B8","Valuation!B10":"='Assumptions'!$B$10","Valuation!B11":"=B9/B10","Valuation!B12":"=MIN('Assumptions'!$B$7,Operating!C32:I32)","Valuation!B15":"=IF('Assumptions'!$B$11=\"\",\"Unavailable\",'Assumptions'!$B$11)","Valuation!B16":"=IF(AND(ISNUMBER(B15),B15&gt;0),B11/B15-1,\"Unavailable\")","Sensitivities!C7":"=MAX(0,'Operating'!$B$4+(-0.02))","Sensitivities!D7":"=MAX(0,'Operating'!$B$4+(0))","Sensitivities!E7":"=MAX(0,'Operating'!$B$4+(0.02))","Sensitivities!C17":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^1","Sensitivities!D17":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^2","Sensitivities!E17":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^3","Sensitivities!F17":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^4","Sensitivities!G17":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^5","Sensitivities!H17":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^6","Sensitivities!I17":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^7","Sensitivities!C8":"=(SUM(C17:I17)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C18":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^1","Sensitivities!D18":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^2","Sensitivities!E18":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^3","Sensitivities!F18":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^4","Sensitivities!G18":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^5","Sensitivities!H18":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^6","Sensitivities!I18":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^7","Sensitivities!D8":"=(SUM(C18:I18)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C19":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^1","Sensitivities!D19":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^2","Sensitivities!E19":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^3","Sensitivities!F19":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^4","Sensitivities!G19":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^5","Sensitivities!H19":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^6","Sensitivities!I19":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^7","Sensitivities!E8":"=(SUM(C19:I19)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C20":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^1","Sensitivities!D20":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^2","Sensitivities!E20":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^3","Sensitivities!F20":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^4","Sensitivities!G20":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^5","Sensitivities!H20":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^6","Sensitivities!I20":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^7","Sensitivities!C9":"=(SUM(C20:I20)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C21":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^1","Sensitivities!D21":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^2","Sensitivities!E21":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^3","Sensitivities!F21":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^4","Sensitivities!G21":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^5","Sensitivities!H21":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^6","Sensitivities!I21":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^7","Sensitivities!D9":"=(SUM(C21:I21)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C22":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^1","Sensitivities!D22":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^2","Sensitivities!E22":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^3","Sensitivities!F22":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^4","Sensitivities!G22":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^5","Sensitivities!H22":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^6","Sensitivities!I22":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^7","Sensitivities!E9":"=(SUM(C22:I22)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C23":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^1","Sensitivities!D23":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^2","Sensitivities!E23":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^3","Sensitivities!F23":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^4","Sensitivities!G23":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^5","Sensitivities!H23":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^6","Sensitivities!I23":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^7","Sensitivities!C10":"=(SUM(C23:I23)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C24":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^1","Sensitivities!D24":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^2","Sensitivities!E24":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^3","Sensitivities!F24":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^4","Sensitivities!G24":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^5","Sensitivities!H24":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^6","Sensitivities!I24":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^7","Sensitivities!D10":"=(SUM(C24:I24)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C25":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^1","Sensitivities!D25":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^2","Sensitivities!E25":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^3","Sensitivities!F25":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^4","Sensitivities!G25":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^5","Sensitivities!H25":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^6","Sensitivities!I25":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^7","Sensitivities!E10":"=(SUM(C25:I25)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Checks!B5":"=IF(OR(Assumptions!B4=\"bear\",Assumptions!B4=\"base\",Assumptions!B4=\"bull\"),\"PASS\",\"FAIL\")","Checks!B6":"=IF('Assumptions'!$B$10&gt;0,\"PASS\",\"FAIL\")","Checks!B7":"=IF(ABS(Valuation!B9-(Valuation!B5+Valuation!B6+Valuation!B7-Valuation!B8))&lt;0.01,\"PASS\",\"FAIL\")","Checks!B8":"=IF(ABS(Sensitivities!D9-Valuation!B11)&lt;0.000001,\"PASS\",\"FAIL\")","Checks!B9":"=IF(OR(AND('Assumptions'!$B$11=\"\",'Assumptions'!$B$13=\"\"),AND(ISNUMBER('Assumptions'!$B$11),'Assumptions'!$B$11&gt;0,'Assumptions'!$B$13&lt;&gt;\"\")),\"PASS\",\"FAIL\")","Checks!B10":"=IF(AND('Operating'!$B$5&gt;=0,'Operating'!$B$5&lt;=1),\"PASS\",\"FAIL\")","Summary!B7":"=Assumptions!B4","Summary!B8":"='Valuation'!$B$11","Summary!B9":"='Valuation'!$B$9","Summary!B10":"='Valuation'!$B$12"}}</t>
+    <t xml:space="preserve">{"schema_version":1,"presentation_version":2,"baseline":{"company_id":"asx-mlx","model_type":"finite_mine","purpose":"illustrative_sensitivity","synthetic":false,"currency":"AUD","valuation_date":"2026-09-20","reference_price":null,"quote_date":null,"cash":374000000,"debt":3285000,"other_assets":0,"diluted_shares":886391538,"historical":[{"entity":"Metals X Group","metric":"cash_and_cash_equivalents","value":293606000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"current_interest_bearing_liabilities","value":2849000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"noncurrent_interest_bearing_liabilities","value":436000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Limited","metric":"issued_ordinary_shares","value":886391538.0,"unit":"shares","currency":null,"period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=62","page":"62","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"rehabilitation_provision_present_value","value":33035000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=60","page":"60","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_operating_cash_flow","value":128323000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_paid_property_plant_equipment","value":13747000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_paid_mine_properties_development","value":22211000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Renison Tin Operation","metric":"tin_in_concentrate_produced","value":10748.0,"unit":"tonnes_tin","currency":null,"period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=9","page":"9","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"ownership_interest","value":0.5,"unit":"fraction","currency":null,"period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"tin_in_concentrate_produced","value":2809.0,"unit":"tonnes_tin","currency":null,"period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"tin_in_concentrate_produced","value":11287.0,"unit":"tonnes_tin","currency":null,"period":"TTM-ended-2026-06-30","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"imputed_tin_price","value":73834.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"imputed_tin_price","value":63760.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"TTM-ended-2026-06-30","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"c1_cash_production_cost","value":20251.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"c1_cash_production_cost","value":19349.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"TTM-ended-2026-06-30","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"imputed_sales_and_marketing_cost","value":8758.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"all_in_sustaining_cost","value":34865.0,"unit":"AUD_per_tonne_tin","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","page":"2","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"capital_expenditure","value":23400000.0,"unit":"AUD","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","page":"3","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"sustaining_capital_expenditure","value":16450000.0,"unit":"AUD","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","page":"3","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Renison Tin Operation","metric":"project_capital_expenditure","value":6950000.0,"unit":"AUD","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","page":"3","basis":"reported","ownership_basis":"whole_operation"},{"entity":"Metals X Group","metric":"cash_and_cash_equivalents","value":374000000.0,"unit":"AUD","currency":"AUD","period":"2026-06-30","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=9","page":"9","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"corporate_costs","value":560000.0,"unit":"AUD","currency":"AUD","period":"2026-Q2","publication_date":"2026-07-27","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","page":"8","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"revenue","value":284999000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"revenue","value":218820000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cost_of_sales","value":158275000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cost_of_sales","value":123558000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"gross_profit","value":126724000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"gross_profit","value":95262000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"general_and_administrative_expenses","value":4212000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"general_and_administrative_expenses","value":2744000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"finance_costs","value":980000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"finance_costs","value":566000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"profit_before_tax","value":138275000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"profit_before_tax","value":120227000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"income_tax_expense","value":33670000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"income_tax_expense","value":17878000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_income","value":104605000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_income","value":102349000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=24","page":"24","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_and_cash_equivalents","value":220644000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"trade_and_other_receivables","value":36473000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"trade_and_other_receivables","value":8666000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"inventories","value":29488000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"inventories","value":37573000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_current_assets","value":363459000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_current_assets","value":271243000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_noncurrent_assets","value":255050000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_noncurrent_assets","value":233789000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_assets","value":618509000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_assets","value":505032000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"trade_and_other_payables","value":17091000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"trade_and_other_payables","value":20972000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"current_interest_bearing_liabilities","value":3645000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"noncurrent_interest_bearing_liabilities","value":2508000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_current_liabilities","value":51679000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_current_liabilities","value":43857000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_noncurrent_liabilities","value":34297000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_noncurrent_liabilities","value":33401000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_liabilities","value":85976000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_liabilities","value":77258000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_equity","value":532533000.0,"unit":"AUD","currency":"AUD","period":"2025-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"total_equity","value":427774000.0,"unit":"AUD","currency":"AUD","period":"2024-12-31","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","page":"25","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_operating_cash_flow","value":143567000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_paid_property_plant_equipment","value":17425000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"cash_paid_mine_properties_development","value":22511000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_investing_cash_flow","value":-52493000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_investing_cash_flow","value":-55453000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_financing_cash_flow","value":-2868000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_financing_cash_flow","value":-10512000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_change_in_cash","value":72962000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"net_change_in_cash","value":77602000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"opening_cash_and_cash_equivalents","value":220644000.0,"unit":"AUD","currency":"AUD","period":"FY2025","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"},{"entity":"Metals X Group","metric":"opening_cash_and_cash_equivalents","value":143042000.0,"unit":"AUD","currency":"AUD","period":"FY2024","publication_date":"2026-03-25","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=26","page":"26","basis":"reported","ownership_basis":"consolidated"}],"scenarios":{"bear":{"discount_rate":0.12,"ownership":0.5,"ownership_basis":"whole_operation","volume_basis":"imputed_production","residual_value":0,"years":[{"year":2027,"payable_tonnes":10158.3,"price":51008,"price_currency":"AUD","fx":1,"unit_cost":30181.8,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2028,"payable_tonnes":10158.3,"price":51008,"price_currency":"AUD","fx":1,"unit_cost":30181.8,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2029,"payable_tonnes":10158.3,"price":51008,"price_currency":"AUD","fx":1,"unit_cost":30181.8,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":100000000,"corporate_cost":2240000}],"notes":"Illustrative 3-year assumed finite horizon; not reserve-backed life. Price multiplier 0.8, unit-cost multiplier 1.1, production proxy multiplier 0.9; not guidance."},"base":{"discount_rate":0.1,"ownership":0.5,"ownership_basis":"whole_operation","volume_basis":"imputed_production","residual_value":0,"years":[{"year":2027,"payable_tonnes":11287,"price":63760,"price_currency":"AUD","fx":1,"unit_cost":27438,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2028,"payable_tonnes":11287,"price":63760,"price_currency":"AUD","fx":1,"unit_cost":27438,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2029,"payable_tonnes":11287,"price":63760,"price_currency":"AUD","fx":1,"unit_cost":27438,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2030,"payable_tonnes":11287,"price":63760,"price_currency":"AUD","fx":1,"unit_cost":27438,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2031,"payable_tonnes":11287,"price":63760,"price_currency":"AUD","fx":1,"unit_cost":27438,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":100000000,"corporate_cost":2240000}],"notes":"Illustrative 5-year assumed finite horizon; not reserve-backed life. Price multiplier 1.0, unit-cost multiplier 1.0, production proxy multiplier 1.0; not guidance."},"bull":{"discount_rate":0.08,"ownership":0.5,"ownership_basis":"whole_operation","volume_basis":"imputed_production","residual_value":0,"years":[{"year":2027,"payable_tonnes":12415.7,"price":76512,"price_currency":"AUD","fx":1,"unit_cost":26066.1,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2028,"payable_tonnes":12415.7,"price":76512,"price_currency":"AUD","fx":1,"unit_cost":26066.1,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2029,"payable_tonnes":12415.7,"price":76512,"price_currency":"AUD","fx":1,"unit_cost":26066.1,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2030,"payable_tonnes":12415.7,"price":76512,"price_currency":"AUD","fx":1,"unit_cost":26066.1,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2031,"payable_tonnes":12415.7,"price":76512,"price_currency":"AUD","fx":1,"unit_cost":26066.1,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2032,"payable_tonnes":12415.7,"price":76512,"price_currency":"AUD","fx":1,"unit_cost":26066.1,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":0,"corporate_cost":2240000},{"year":2033,"payable_tonnes":12415.7,"price":76512,"price_currency":"AUD","fx":1,"unit_cost":26066.1,"royalty_rate":0,"tax_rate":0.3,"depreciation":0,"capex":93600000,"working_capital_change":0,"closure":100000000,"corporate_cost":2240000}],"notes":"Illustrative 7-year assumed finite horizon; not reserve-backed life. Price multiplier 1.2, unit-cost multiplier 0.95, production proxy multiplier 1.1; not guidance."}},"provenance":{"/cash":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-conten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=9","rationale":"Reported group closing cash June 30 2026; no ownership scaling; stale at valuation date.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/debt":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=25","rationale":"Sum current 2,849,000 and noncurrent 436,000 financing liabilities at Dec 31 2025; stale proxy, not a verified current bridge.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/other_assets":{"unit":"AUD","source":"analyst-assumption://limited-sensitivity","rationale":"Exclude other investments/residual assets from this limited model; not a statement of zero economic value.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/diluted_shares":{"unit":"shares","source":"https://www.metalsx.com.au/wp-content/uploads/2026/03/MLX-Annual-Report-31-December-2025.pdf#page=62","rationale":"Issued-share denominator Dec 31 2025, NOT verified current diluted shares; illustrative only.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/discount_rate":{"unit":"fraction","source":"analyst-assumption://discount-rate","rationale":"Illustrative discount rate; not a derived company WACC.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/ownership":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"Reported 50% ownership of Renison; apply once to whole-operation FCF.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/residual_value":{"unit":"AUD","source":"analyst-assumption://finite-horizon","rationale":"No terminal perpetuity or residual asset value; horizon is an unverified stress assumption.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×0.9; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×0.8; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.1; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/0/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×0.9; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×0.8; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.1; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/1/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×0.9; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×0.8; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.1; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bear/years/2/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/discount_rate":{"unit":"fraction","source":"analyst-assumption://discount-rate","rationale":"Illustrative discount rate; not a derived company WACC.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/ownership":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"Reported 50% ownership of Renison; apply once to whole-operation FCF.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/residual_value":{"unit":"AUD","source":"analyst-assumption://finite-horizon","rationale":"No terminal perpetuity or residual asset value; horizon is an unverified stress assumption.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/0/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/1/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/2/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ing and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/3/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.0; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.0; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×1.0; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/base/years/4/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/discount_rate":{"unit":"fraction","source":"analyst-assumption://discount-rate","rationale":"Illustrative discount rate; not a derived company WACC.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/ownership":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"Reported 50% ownership of Renison; apply once to whole-operation FCF.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/residual_value":{"unit":"AUD","source":"analyst-assumption://finite-horizon","rationale":"No terminal perpetuity or residual asset value; horizon is an unverified stress assumption.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/0/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/1/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/2/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/3/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/4/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/5/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/payable_tonnes":{"unit":"tonnes","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM produced 11,287t ×1.1; IMPUTED PRODUCTION PROXY only, not payable sales. Gross imputed revenue includes 100% produced and marketing cost deducts payable tin charges.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/price":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"TTM LME-imputed AUD 63,760/t ×1.2; not realized price, no claim of forecast guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/fx":{"unit":"AUD/AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"All imputed price/costs reported in AUD; identity conversion.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/unit_cost":{"unit":"AUD/tonne","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=2","rationale":"(TTM C 1 19,349 + imputed sales/marketing 8,089) ×0.95; includes royalties/payable deductions. Assumed future run-rate, not guidance.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/royalty_rate":{"unit":"fraction","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Royalties already inside imputed sales/marketing; zero additional charge avoids double counting.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/tax_rate":{"unit":"fraction","source":"analyst-assumption://simplified-tax","rationale":"Assume 30% tax on positive cash-based EBIT; no depreciation shields/losses. Not a verified fiscal forecast.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/depreciation":{"unit":"AUD","source":"analyst-assumption://no-tax-depreciation","rationale":"Assume no depreciation tax shield; uncertain taxable bases need reconciliation.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/capex":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=3","rationale":"Annualize total whole-operation quarterly 23.4m ×4, includes sustaining and project spend; illustrative, no AISC double deduction.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/working_capital_change":{"unit":"AUD","source":"analyst-assumption://flat-working-capital","rationale":"Assume zero annual change solely for sensitivity; inventory/receivables timing is not established.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/closure":{"unit":"AUD","source":"analyst-assumption://nominal-closure","rationale":"Assume nominal whole-operation 100m at final model year; zero earlier payments assumed. Not the reported discounted accounting provision.","author":"Agent-authored public example; reported source or explicit assumption as described"},"/scenarios/bull/years/6/corporate_cost":{"unit":"AUD","source":"https://www.metalsx.com.au/wp-content/uploads/2026/07/02_MLX_Quarterly-Report_30-June-2026_Final.pdf#page=8","rationale":"Annualized group quarterly 0.56m ×4; deducted after ownership scaling, not scaled again.","author":"Agent-authored public example; reported source or explicit assumption as described"}},"known_limitations":["ILLUSTRATIVE IMPUTED-REVENUE SENSITIVITY ONLY. This is not an actionable fair-value estimate or an investment recommendation.","Production is used solely as the company-style imputed-revenue proxy (100% produced tin sold/paid); it is NOT reported payable sales. The workbook labels it production_tonnes_proxy. Realized payable sales, inventory, settlement timing and revenue must replace this proxy before valuation.","The baseline price AUD63,760/t is the reported trailing-12-month LME-imputed price, NOT realized tin sales price. Scenario price and volume levels are analyst stress assumptions, not company guidance.","Unit cost combines reported trailing-12-month C1 AUD19,349/t and imputed sales/marketing AUD8,089/t. Marketing includes royalties and payable-tin deductions, so separate royalty_rate=0 prevents duplicate deductions. Price-linked marketing behavior is not separately modelled and could materially affect sensitivity.","Finite horizons 3/5/7 years are illustrative assumptions, not reserve-supported mine life. The quarterly report said an updated life-of-mine plan and Ore Reserve were expected in Q3 2026; those updates have not been verified. No perpetuity or residual value is included.","Cash AUD374m is as at June 30 2026; debt AUD3.285m and issued shares886,391,538 are as at December31 2025. These stale mixed-date balances need updated half-year/ASX checks. Issued shares are a proxy, NOT a verified current fully diluted denominator.","Closure is an explicit assumed AUD100m whole-operation nominal final-year payment. The reported AUD33.035m group rehabilitation provision is a present-value accounting figure, not this cash-payment estimate; actual scope/timing and other closure sites remain unmodelled.","Capex annualizes June-quarter whole-operation AUD23.4m to AUD93.6m each model year, including both sustaining and project spend. This is a scenario assumption, not guidance. No additional AISC deduction is made.","Annual corporate costs annualize group June-quarter AUD0.56m to AUD2.24m, deducted once after 50% attribution. Other investments/residual assets are set to zero only to exclude them from this limited sensitivity, not because they have zero economic value.","Tax rate30% is an analyst simplifying assumption; depreciation is assumed zero and no loss carryforwards, corporate tax shields or closure deductions are modelled. No forecast working-capital changes are assumed; this is not verified operational guidance.","Annual row labels2027 onward denote period-end annualized flows one/two/etc years from the valuation date, not an audited fiscal calendar projection. No remaining2026 stub cash flow is forecast. Forecast years are constant run-rate proxies.","No verified current share quote is supplied. Reverse valuation and price/upside comparisons are unavailable. No actual user portfolio is used.","Historical statement summaries now include FY2025 and FY2024 as reported in the 2025 annual report. This is a selected comparative history, not a full three-year normalization or a linked three-statement forecast. Group consolidated actuals must not be compared directly with unscaled whole-operation model rows."],"notes":"Public worked example. Reported historical figures are transcribed from issuer documents; future inputs are agent-authored illustrative assumptions, not management guidance. See MLX-MODEL-NOTES.md for source-page mapping, sign conventions and reconciliation checks."},"inputs":{"/cash":{"sheet":"Assumptions","cell":"B7"},"/debt":{"sheet":"Assumptions","cell":"B8"},"/other_assets":{"sheet":"Assumptions","cell":"B9"},"/diluted_shares":{"sheet":"Assumptions","cell":"B10"},"/reference_price":{"sheet":"Assumptions","cell":"B11"},"/valuation_date":{"sheet":"Assumptions","cell":"B12"},"/quote_date":{"sheet":"Assumptions","cell":"B13"},"/scenarios/bear/discount_rate":{"sheet":"Assumptions","cell":"B20"},"/scenarios/bear/ownership":{"sheet":"Assumptions","cell":"B21"},"/scenarios/bear/residual_value":{"sheet":"Assumptions","cell":"B22"},"/scenarios/bear/years/0/payable_tonnes":{"sheet":"Assumptions","cell":"C25"},"/scenarios/bear/years/1/payable_tonnes":{"sheet":"Assumptions","cell":"D25"},"/scenarios/bear/years/2/payable_tonnes":{"sheet":"Assumptions","cell":"E25"},"/scenarios/bear/years/0/price":{"sheet":"Assumptions","cell":"C26"},"/scenarios/bear/years/1/price":{"sheet":"Assumptions","cell":"D26"},"/scenarios/bear/years/2/price":{"sheet":"Assumptions","cell":"E26"},"/scenarios/bear/years/0/fx":{"sheet":"Assumptions","cell":"C27"},"/scenarios/bear/years/1/fx":{"sheet":"Assumptions","cell":"D27"},"/scenarios/bear/years/2/fx":{"sheet":"Assumptions","cell":"E27"},"/scenarios/bear/years/0/unit_cost":{"sheet":"Assumptions","cell":"C28"},"/scenarios/bear/years/1/unit_cost":{"sheet":"Assumptions","cell":"D28"},"/scenarios/bear/years/2/unit_cost":{"sheet":"Assumptions","cell":"E28"},"/scenarios/bear/years/0/royalty_rate":{"sheet":"Assumptions","cell":"C29"},"/scenarios/bear/years/1/royalty_rate":{"sheet":"Assumptions","cell":"D29"},"/scenarios/bear/years/2/royalty_rate":{"sheet":"Assumptions","cell":"E29"},"/scenarios/bear/years/0/tax_rate":{"sheet":"Assumptions","cell":"C30"},"/scenarios/bear/years/1/tax_rate":{"sheet":"Assumptions","cell":"D30"},"/scenarios/bear/years/2/tax_rate":{"sheet":"Assumptions","cell":"E30"},"/scenarios/bear/years/0/depreciation":{"sheet":"Assumptions","cell":"C31"},"/scenarios/bear/years/1/depreciation":{"sheet":"Assumptions","cell":"D31"},"/scenarios/bear/years/2/depreciation":{"sheet":"Assumptions","cell":"E31"},"/scenarios/bear/years/0/capex":{"sheet":"Assumptions","cell":"C32"},"/scenarios/bear/years/1/capex":{"sheet":"Assumptions","cell":"D32"},"/scenarios/bear/years/2/capex":{"sheet":"Assumptions","cell":"E32"},"/scenarios/bear/years/0/working_capital_change":{"sheet":"Assumptions","cell":"C33"},"/scenarios/bear/years/1/working_capital_change":{"sheet":"Assumptions","cell":"D33"},"/scenarios/bear/years/2/working_capital_change":{"sheet":"Assumptions","cell":"E33"},"/scenarios/bear/years/0/closure":{"sheet":"Assumptions","cell":"C34"},"/scenarios/bear/years/1/closure":{"sheet":"Assumptions","cell":"D34"},"/scenarios/bear/years/2/closure":{"sheet":"Assumptions","cell":"E34"},"/scenarios/bear/years/0/corporate_cost":{"sheet":"Assumptions","cell":"C35"},"/scenarios/bear/years/1/corporate_cost":{"sheet":"Assumptions","cell":"D35"},"/scenarios/bear/years/2/corporate_cost":{"sheet":"Assumptions","cell":"E35"},"/scenarios/base/discount_rate":{"sheet":"Assumptions","cell":"B39"},"/scenarios/base/ownership":{"sheet":"Assumptions","cell":"B40"},"/scenarios/base/residual_value":{"sheet":"Assumptions","cell":"B41"},"/scenarios/base/years/0/payable_tonnes":{"sheet":"Assumptions","cell":"C44"},"/scenarios/base/years/1/payable_tonnes":{"sheet":"Assumptions","cell":"D44"},"/scenarios/base/years/2/payable_tonnes":{"sheet":"Assumptions","cell":"E44"},"/scenarios/base/years/3/payable_tonnes":{"sheet":"Assumptions","cell":"F44"},"/scenarios/base/years/4/payable_tonnes":{"sheet":"Assumptions","cell":"G44"},"/scenarios/base/years/0/price":{"sheet":"Assumptions","cell":"C45"},"/scenarios/base/years/1/price":{"sheet":"Assumptions","cell":"D45"},"/scenarios/base/years/2/price":{"sheet":"Assumptions","cell":"E45"},"/scenarios/base/years/3/price":{"sheet":"Assumptions","cell":"F45"},"/scenarios/base/years/4/price":{"sheet":"Assumptions","cell":"G45"},"/scenarios/base/years/0/fx":{"sheet":"Assumptions","cell":"C46"},"/scenarios/base/years/1/fx":{"sheet":"Assumptions","cell":"D46"},"/scenarios/base/years/2/fx":{"sheet":"Assumptions","cell":"E46"},"/scenarios/base/years/3/fx":{"sheet":"Assumptions","cell":"F46"},"/scenarios/base/years/4/fx":{"sheet":"Assumptions","cell":"G46"},"/scenarios/base/years/0/unit_cost":{"sheet":"Assumptions","cell":"C47"},"/scenarios/base/years/1/unit_cost":{"sheet":"Assumptions","cell":"D47"},"/scenarios/base/years/2/unit_cost":{"sheet":"Assumptions","cell":"E47"},"/scenarios/base/years/3/unit_cost":{"sheet":"Assumptions","cell":"F47"},"/scenarios/base/years/4/unit_cost":{"sheet":"Assumptions","cell":"G47"},"/scenarios/base/years/0/royalty_rate":{"sheet":"Assumptions","cell":"C48"},"/scenarios/base/years/1/royalty_rate":{"sheet":"Assumptions","cell":"D48"},"/scenarios/base/years/2/royalty_rate":{"sheet":"Assumptions","cell":"E48"},"/scenarios/base/years/3/royalty_rate":{"sheet":"Assumptions","cell":"F48"},"/scenarios/base/years/4/royalty_rate":{"sheet":"Assumptions","cell":"G48"},"/scenarios/base/years/0/tax_rate":{"sheet":"Assumptions","cell":"C49"},"/scenarios/base/years/1/tax_rate":{"sheet":"Assumptions","cell":"D49"},"/scenarios/base/years/2/tax_rate":{"sheet":"Assumptions","cell":"E49"},"/scenarios/base/years/3/tax_rate":{"sheet":"Assumptions","cell":"F49"},"/scenarios/base/years/4/tax_rate":{"sheet":"Assumptions","cell":"G49"},"/scenarios/base/years/0/depreciation":{"sheet":"Assumptions","cell":"C50"},"/scenarios/base/years/1/depreciation":{"sheet":"Assumptions","cell":"D50"},"/scenarios/base/years/2/depreciation":{"sheet":"Assumptions","cell":"E50"},"/scenarios/base/years/3/depreciation":{"sheet":"Assumptions","cell":"F50"},"/scenarios/base/years/4/depreciation":{"sheet":"Assumptions","cell":"G50"},"/scenarios/base/years/0/capex":{"sheet":"Assumptions","cell":"C51"},"/scenarios/base/years/1/capex":{"sheet":"Assumptions","cell":"D51"},"/scenarios/base/years/2/capex":{"sheet":"Assumptions","cell":"E51"},"/scenarios/base/years/3/capex":{"sheet":"Assumptions","cell":"F51"},"/scenarios/base/years/4/capex":{"sheet":"Assumptions","cell":"G51"},"/scenarios/base/years/0/working_capital_change":{"sheet":"Assumptions","cell":"C52"},"/scenarios/base/years/1/working_capital_change":{"sheet":"Assumptions","cell":"D52"},"/scenarios/base/years/2/working_capital_change":{"sheet":"Assumptions","cell":"E52"},"/scenarios/base/years/3/working_capital_change":{"sheet":"Assumptions","cell":"F52"},"/scenarios/base/years/4/working_capital_change":{"sheet":"Assumptions","cell":"G52"},"/scenarios/base/years/0/closure":{"sheet":"Assumptions","cell":"C53"},"/scenarios/base/years/1/closure":{"sheet":"Assumptions","cell":"D53"},"/scenarios/base/years/2/closure":{"sheet":"Assumptions","cell":"E53"},"/scenarios/base/years/3/closure":{"sheet":"Assumptions","cell":"F53"},"/scenarios/base/years/4/closure":{"sheet":"Assumptions","cell":"G53"},"/scenarios/base/years/0/corporate_cost":{"sheet":"Assumptions","cell":"C54"},"/scenarios/base/years/1/corporate_cost":{"sheet":"Assumptions","cell":"D54"},"/scenarios/base/years/2/corporate_cost":{"sheet":"Assumptions","cell":"E54"},"/scenarios/base/years/3/corporate_cost":{"sheet":"Assumptions","cell":"F54"},"/scenarios/base/years/4/corporate_cost":{"sheet":"Assumptions","cell":"G54"},"/scenarios/bull/discount_rate":{"sheet":"Assumptions","cell":"B58"},"/scenarios/bull/ownership":{"sheet":"Assumptions","cell":"B59"},"/scenarios/bull/residual_value":{"sheet":"Assumptions","cell":"B60"},"/scenarios/bull/years/0/payable_tonnes":{"sheet":"Assumptions","cell":"C63"},"/scenarios/bull/years/1/payable_tonnes":{"sheet":"Assumptions","cell":"D63"},"/scenarios/bull/years/2/payable_tonnes":{"sheet":"Assumptions","cell":"E63"},"/scenarios/bull/years/3/payable_tonnes":{"sheet":"Assumptions","cell":"F63"},"/scenarios/bull/years/4/payable_tonnes":{"sheet":"Assumptions","cell":"G63"},"/scenarios/bull/years/5/payable_tonnes":{"sheet":"Assumptions","cell":"H63"},"/scenarios/bull/years/6/payable_tonnes":{"sheet":"Assumptions","cell":"I63"},"/scenarios/bull/years/0/price":{"sheet":"Assumptions","cell":"C64"},"/scenarios/bull/years/1/price":{"sheet":"Assumptions","cell":"D64"},"/scenarios/bull/years/2/price":{"sheet":"Assumptions","cell":"E64"},"/scenarios/bull/years/3/price":{"sheet":"Assumptions","cell":"F64"},"/scenarios/bull/years/4/price":{"sheet":"Assumptions","cell":"G64"},"/scenarios/bull/years/5/price":{"sheet":"Assumptions","cell":"H64"},"/scenarios/bull/years/6/price":{"sheet":"Assumptions","cell":"I64"},"/scenarios/bull/years/0/fx":{"sheet":"Assumptions","cell":"C65"},"/scenarios/bull/years/1/fx":{"sheet":"Assumptions","cell":"D65"},"/scenarios/bull/years/2/fx":{"sheet":"Assumptions","cell":"E65"},"/scenarios/bull/years/3/fx":{"sheet":"Assumptions","cell":"F65"},"/scenarios/bull/years/4/fx":{"sheet":"Assumptions","cell":"G65"},"/scenarios/bull/years/5/fx":{"sheet":"Assumptions","cell":"H65"},"/scenarios/bull/years/6/fx":{"sheet":"Assumptions","cell":"I65"},"/scenarios/bull/years/0/unit_cost":{"sheet":"Assumptions","cell":"C66"},"/scenarios/bull/years/1/unit_cost":{"sheet":"Assumptions","cell":"D66"},"/scenarios/bull/years/2/unit_cost":{"sheet":"Assumptions","cell":"E66"},"/scenarios/bull/years/3/unit_cost":{"sheet":"Assumptions","cell":"F66"},"/scenarios/bull/years/4/unit_cost":{"sheet":"Assumptions","cell":"G66"},"/scenarios/bull/years/5/unit_cost":{"sheet":"Assumptions","cell":"H66"},"/scenarios/bull/years/6/unit_cost":{"sheet":"Assumptions","cell":"I66"},"/scenarios/bull/years/0/royalty_rate":{"sheet":"Assumptions","cell":"C67"},"/scenarios/bull/years/1/royalty_rate":{"sheet":"Assumptions","cell":"D67"},"/scenarios/bull/years/2/royalty_rate":{"sheet":"Assumptions","cell":"E67"},"/scenarios/bull/years/3/royalty_rate":{"sheet":"Assumptions","cell":"F67"},"/scenarios/bull/years/4/royalty_rate":{"sheet":"Assumptions","cell":"G67"},"/scenarios/bull/years/5/royalty_rate":{"sheet":"Assumptions","cell":"H67"},"/scenarios/bull/years/6/royalty_rate":{"sheet":"Assumptions","cell":"I67"},"/scenarios/bull/years/0/tax_rate":{"sheet":"Assumptions","cell":"C68"},"/scenarios/bull/years/1/tax_rate":{"sheet":"Assumptions","cell":"D68"},"/scenarios/bull/years/2/tax_rate":{"sheet":"Assumptions","cell":"E68"},"/scenarios/bull/years/3/tax_rate":{"sheet":"Assumptions","cell":"F68"},"/scenarios/bull/years/4/tax_rate":{"sheet":"Assumptions","cell":"G68"},"/scenarios/bull/years/5/tax_rate":{"sheet":"Assumptions","cell":"H68"},"/scenarios/bull/years/6/tax_rate":{"sheet":"Assumptions","cell":"I68"},"/scenarios/bull/years/0/depreciation":{"sheet":"Assumptions","cell":"C69"},"/scenarios/bull/years/1/depreciation":{"sheet":"Assumptions","cell":"D69"},"/scenarios/bull/years/2/depreciation":{"sheet":"Assumptions","cell":"E69"},"/scenarios/bull/years/3/depreciation":{"sheet":"Assumptions","cell":"F69"},"/scenarios/bull/years/4/depreciation":{"sheet":"Assumptions","cell":"G69"},"/scenarios/bull/years/5/depreciation":{"sheet":"Assumptions","cell":"H69"},"/scenarios/bull/years/6/depreciation":{"sheet":"Assumptions","cell":"I69"},"/scenarios/bull/years/0/capex":{"sheet":"Assumptions","cell":"C70"},"/scenarios/bull/years/1/capex":{"sheet":"Assumptions","cell":"D70"},"/scenarios/bull/years/2/capex":{"sheet":"Assumptions","cell":"E70"},"/scenarios/bull/years/3/capex":{"sheet":"Assumptions","cell":"F70"},"/scenarios/bull/years/4/capex":{"sheet":"Assumptions","cell":"G70"},"/scenarios/bull/years/5/capex":{"sheet":"Assumptions","cell":"H70"},"/scenarios/bull/years/6/capex":{"sheet":"Assumptions","cell":"I70"},"/scenarios/bull/years/0/working_capital_change":{"sheet":"Assumptions","cell":"C71"},"/scenarios/bull/years/1/working_capital_change":{"sheet":"Assumptions","cell":"D71"},"/scenarios/bull/years/2/working_capital_change":{"sheet":"Assumptions","cell":"E71"},"/scenarios/bull/years/3/working_capital_change":{"sheet":"Assumptions","cell":"F71"},"/scenarios/bull/years/4/working_capital_change":{"sheet":"Assumptions","cell":"G71"},"/scenarios/bull/years/5/working_capital_change":{"sheet":"Assumptions","cell":"H71"},"/scenarios/bull/years/6/working_capital_change":{"sheet":"Assumptions","cell":"I71"},"/scenarios/bull/years/0/closure":{"sheet":"Assumptions","cell":"C72"},"/scenarios/bull/years/1/closure":{"sheet":"Assumptions","cell":"D72"},"/scenarios/bull/years/2/closure":{"sheet":"Assumptions","cell":"E72"},"/scenarios/bull/years/3/closure":{"sheet":"Assumptions","cell":"F72"},"/scenarios/bull/years/4/closure":{"sheet":"Assumptions","cell":"G72"},"/scenarios/bull/years/5/closure":{"sheet":"Assumptions","cell":"H72"},"/scenarios/bull/years/6/closure":{"sheet":"Assumptions","cell":"I72"},"/scenarios/bull/years/0/corporate_cost":{"sheet":"Assumptions","cell":"C73"},"/scenarios/bull/years/1/corporate_cost":{"sheet":"Assumptions","cell":"D73"},"/scenarios/bull/years/2/corporate_cost":{"sheet":"Assumptions","cell":"E73"},"/scenarios/bull/years/3/corporate_cost":{"sheet":"Assumptions","cell":"F73"},"/scenarios/bull/years/4/corporate_cost":{"sheet":"Assumptions","cell":"G73"},"/scenarios/bull/years/5/corporate_cost":{"sheet":"Assumptions","cell":"H73"},"/scenarios/bull/years/6/corporate_cost":{"sheet":"Assumptions","cell":"I73"}},"outputs":{"active_case":{"sheet":"Assumptions","cell":"B4"},"years/0/year":{"sheet":"Operating","cell":"C9"},"years/0/revenue":{"sheet":"Operating","cell":"C23"},"years/0/operating_cost":{"sheet":"Operating","cell":"C24"},"years/0/royalties":{"sheet":"Operating","cell":"C25"},"years/0/ebit":{"sheet":"Operating","cell":"C26"},"years/0/tax":{"sheet":"Operating","cell":"C27"},"years/0/nopat":{"sheet":"Operating","cell":"C28"},"years/0/operating_fcf":{"sheet":"Operating","cell":"C29"},"years/0/fcf":{"sheet":"Operating","cell":"C30"},"years/0/present_value":{"sheet":"Operating","cell":"C31"},"years/0/illustrative_cash":{"sheet":"Operating","cell":"C32"},"years/1/year":{"sheet":"Operating","cell":"D9"},"years/1/revenue":{"sheet":"Operating","cell":"D23"},"years/1/operating_cost":{"sheet":"Operating","cell":"D24"},"years/1/royalties":{"sheet":"Operating","cell":"D25"},"years/1/ebit":{"sheet":"Operating","cell":"D26"},"years/1/tax":{"sheet":"Operating","cell":"D27"},"years/1/nopat":{"sheet":"Operating","cell":"D28"},"years/1/operating_fcf":{"sheet":"Operating","cell":"D29"},"years/1/fcf":{"sheet":"Operating","cell":"D30"},"years/1/present_value":{"sheet":"Operating","cell":"D31"},"years/1/illustrative_cash":{"sheet":"Operating","cell":"D32"},"years/2/year":{"sheet":"Operating","cell":"E9"},"years/2/revenue":{"sheet":"Operating","cell":"E23"},"years/2/operating_cost":{"sheet":"Operating","cell":"E24"},"years/2/royalties":{"sheet":"Operating","cell":"E25"},"years/2/ebit":{"sheet":"Operating","cell":"E26"},"years/2/tax":{"sheet":"Operating","cell":"E27"},"years/2/nopat":{"sheet":"Operating","cell":"E28"},"years/2/operating_fcf":{"sheet":"Operating","cell":"E29"},"years/2/fcf":{"sheet":"Operating","cell":"E30"},"years/2/present_value":{"sheet":"Operating","cell":"E31"},"years/2/illustrative_cash":{"sheet":"Operating","cell":"E32"},"years/3/year":{"sheet":"Operating","cell":"F9"},"years/3/revenue":{"sheet":"Operating","cell":"F23"},"years/3/operating_cost":{"sheet":"Operating","cell":"F24"},"years/3/royalties":{"sheet":"Operating","cell":"F25"},"years/3/ebit":{"sheet":"Operating","cell":"F26"},"years/3/tax":{"sheet":"Operating","cell":"F27"},"years/3/nopat":{"sheet":"Operating","cell":"F28"},"years/3/operating_fcf":{"sheet":"Operating","cell":"F29"},"years/3/fcf":{"sheet":"Operating","cell":"F30"},"years/3/present_value":{"sheet":"Operating","cell":"F31"},"years/3/illustrative_cash":{"sheet":"Operating","cell":"F32"},"years/4/year":{"sheet":"Operating","cell":"G9"},"years/4/revenue":{"sheet":"Operating","cell":"G23"},"years/4/operating_cost":{"sheet":"Operating","cell":"G24"},"years/4/royalties":{"sheet":"Operating","cell":"G25"},"years/4/ebit":{"sheet":"Operating","cell":"G26"},"years/4/tax":{"sheet":"Operating","cell":"G27"},"years/4/nopat":{"sheet":"Operating","cell":"G28"},"years/4/operating_fcf":{"sheet":"Operating","cell":"G29"},"years/4/fcf":{"sheet":"Operating","cell":"G30"},"years/4/present_value":{"sheet":"Operating","cell":"G31"},"years/4/illustrative_cash":{"sheet":"Operating","cell":"G32"},"years/5/year":{"sheet":"Operating","cell":"H9"},"years/5/revenue":{"sheet":"Operating","cell":"H23"},"years/5/operating_cost":{"sheet":"Operating","cell":"H24"},"years/5/royalties":{"sheet":"Operating","cell":"H25"},"years/5/ebit":{"sheet":"Operating","cell":"H26"},"years/5/tax":{"sheet":"Operating","cell":"H27"},"years/5/nopat":{"sheet":"Operating","cell":"H28"},"years/5/operating_fcf":{"sheet":"Operating","cell":"H29"},"years/5/fcf":{"sheet":"Operating","cell":"H30"},"years/5/present_value":{"sheet":"Operating","cell":"H31"},"years/5/illustrative_cash":{"sheet":"Operating","cell":"H32"},"years/6/year":{"sheet":"Operating","cell":"I9"},"years/6/revenue":{"sheet":"Operating","cell":"I23"},"years/6/operating_cost":{"sheet":"Operating","cell":"I24"},"years/6/royalties":{"sheet":"Operating","cell":"I25"},"years/6/ebit":{"sheet":"Operating","cell":"I26"},"years/6/tax":{"sheet":"Operating","cell":"I27"},"years/6/nopat":{"sheet":"Operating","cell":"I28"},"years/6/operating_fcf":{"sheet":"Operating","cell":"I29"},"years/6/fcf":{"sheet":"Operating","cell":"I30"},"years/6/present_value":{"sheet":"Operating","cell":"I31"},"years/6/illustrative_cash":{"sheet":"Operating","cell":"I32"},"enterprise_value":{"sheet":"Valuation","cell":"B5"},"cash":{"sheet":"Valuation","cell":"B6"},"other_assets":{"sheet":"Valuation","cell":"B7"},"debt":{"sheet":"Valuation","cell":"B8"},"equity_value":{"sheet":"Valuation","cell":"B9"},"diluted_shares":{"sheet":"Valuation","cell":"B10"},"per_share":{"sheet":"Valuation","cell":"B11"},"minimum_illustrative_cash":{"sheet":"Valuation","cell":"B12"},"discount_rate/0":{"sheet":"Sensitivities","cell":"C7"},"discount_rate/1":{"sheet":"Sensitivities","cell":"D7"},"discount_rate/2":{"sheet":"Sensitivities","cell":"E7"},"driver_multiplier/0":{"sheet":"Sensitivities","cell":"B8"},"sensitivity/0/0":{"sheet":"Sensitivities","cell":"C8"},"sensitivity/0/1":{"sheet":"Sensitivities","cell":"D8"},"sensitivity/0/2":{"sheet":"Sensitivities","cell":"E8"},"driver_multiplier/1":{"sheet":"Sensitivities","cell":"B9"},"sensitivity/1/0":{"sheet":"Sensitivities","cell":"C9"},"sensitivity/1/1":{"sheet":"Sensitivities","cell":"D9"},"sensitivity/1/2":{"sheet":"Sensitivities","cell":"E9"},"driver_multiplier/2":{"sheet":"Sensitivities","cell":"B10"},"sensitivity/2/0":{"sheet":"Sensitivities","cell":"C10"},"sensitivity/2/1":{"sheet":"Sensitivities","cell":"D10"},"sensitivity/2/2":{"sheet":"Sensitivities","cell":"E10"},"checks/0":{"sheet":"Checks","cell":"B5"},"checks/1":{"sheet":"Checks","cell":"B6"},"checks/2":{"sheet":"Checks","cell":"B7"},"checks/3":{"sheet":"Checks","cell":"B8"},"checks/4":{"sheet":"Checks","cell":"B9"},"checks/5":{"sheet":"Checks","cell":"B10"}},"formula_cells":{"Operating!B4":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$B$20,IF(Assumptions!$B$4=\"base\",'Assumptions'!$B$39,'Assumptions'!$B$58))","Operating!B5":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$B$21,IF(Assumptions!$B$4=\"base\",'Assumptions'!$B$40,'Assumptions'!$B$59))","Operating!B6":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$B$22,IF(Assumptions!$B$4=\"base\",'Assumptions'!$B$41,'Assumptions'!$B$60))","Operating!B7":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$B$23,IF(Assumptions!$B$4=\"base\",'Assumptions'!$B$42,'Assumptions'!$B$61))","Operating!B8":"=IF(Assumptions!$B$4=\"bear\",\"imputed_production\",IF(Assumptions!$B$4=\"base\",\"imputed_production\",\"imputed_production\"))","Operating!C9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+1","Operating!C10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$44,'Assumptions'!$C$63))","Operating!C11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$45,'Assumptions'!$C$64))","Operating!C12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$46,'Assumptions'!$C$65))","Operating!C13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$47,'Assumptions'!$C$66))","Operating!C14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$48,'Assumptions'!$C$67))","Operating!C15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$49,'Assumptions'!$C$68))","Operating!C16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$50,'Assumptions'!$C$69))","Operating!C17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$51,'Assumptions'!$C$70))","Operating!C18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$52,'Assumptions'!$C$71))","Operating!C19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$53,'Assumptions'!$C$72))","Operating!C20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$C$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$C$54,'Assumptions'!$C$73))","Operating!C23":"='Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12","Operating!C24":"='Operating'!$C$10*'Operating'!$C$13","Operating!C25":"='Operating'!$C$23*'Operating'!$C$14","Operating!C26":"='Operating'!$C$23-'Operating'!$C$24-'Operating'!$C$25-'Operating'!$C$16","Operating!C27":"=MAX(0,'Operating'!$C$26)*'Operating'!$C$15","Operating!C28":"='Operating'!$C$26-'Operating'!$C$27","Operating!C29":"='Operating'!$C$28+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19","Operating!C30":"='Operating'!$C$29*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0)","Operating!C31":"='Operating'!$C$30/(1+'Operating'!$B$4)^1","Operating!C32":"='Assumptions'!$B$7+'Operating'!$C$30","Operating!D9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+2","Operating!D10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$44,'Assumptions'!$D$63))","Operating!D11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$45,'Assumptions'!$D$64))"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">,"Operating!D12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$46,'Assumptions'!$D$65))","Operating!D13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$47,'Assumptions'!$D$66))","Operating!D14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$48,'Assumptions'!$D$67))","Operating!D15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$49,'Assumptions'!$D$68))","Operating!D16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$50,'Assumptions'!$D$69))","Operating!D17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$51,'Assumptions'!$D$70))","Operating!D18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$52,'Assumptions'!$D$71))","Operating!D19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$53,'Assumptions'!$D$72))","Operating!D20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$D$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$D$54,'Assumptions'!$D$73))","Operating!D23":"='Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12","Operating!D24":"='Operating'!$D$10*'Operating'!$D$13","Operating!D25":"='Operating'!$D$23*'Operating'!$D$14","Operating!D26":"='Operating'!$D$23-'Operating'!$D$24-'Operating'!$D$25-'Operating'!$D$16","Operating!D27":"=MAX(0,'Operating'!$D$26)*'Operating'!$D$15","Operating!D28":"='Operating'!$D$26-'Operating'!$D$27","Operating!D29":"='Operating'!$D$28+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19","Operating!D30":"='Operating'!$D$29*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0)","Operating!D31":"='Operating'!$D$30/(1+'Operating'!$B$4)^2","Operating!D32":"='Operating'!$C$32+'Operating'!$D$30","Operating!E9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+3","Operating!E10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$44,'Assumptions'!$E$63))","Operating!E11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$45,'Assumptions'!$E$64))","Operating!E12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$46,'Assumptions'!$E$65))","Operating!E13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$47,'Assumptions'!$E$66))","Operating!E14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$48,'Assumptions'!$E$67))","Operating!E15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$49,'Assumptions'!$E$68))","Operating!E16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$50,'Assumptions'!$E$69))","Operating!E17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$51,'Assumptions'!$E$70))","Operating!E18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$52,'Assumptions'!$E$71))","Operating!E19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$53,'Assumptions'!$E$72))","Operating!E20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$E$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$E$54,'Assumptions'!$E$73))","Operating!E23":"='Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12","Operating!E24":"='Operating'!$E$10*'Operating'!$E$13","Operating!E25":"='Operating'!$E$23*'Operating'!$E$14","Operating!E26":"='Operating'!$E$23-'Operating'!$E$24-'Operating'!$E$25-'Operating'!$E$16","Operating!E27":"=MAX(0,'Operating'!$E$26)*'Operating'!$E$15","Operating!E28":"='Operating'!$E$26-'Operating'!$E$27","Operating!E29":"='Operating'!$E$28+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19","Operating!E30":"='Operating'!$E$29*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0)","Operating!E31":"='Operating'!$E$30/(1+'Operating'!$B$4)^3","Operating!E32":"='Operating'!$D$32+'Operating'!$E$30","Operating!F9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+4","Operating!F10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$44,'Assumptions'!$F$63))","Operating!F11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$45,'Assumptions'!$F$64))","Operating!F12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$46,'Assumptions'!$F$65))","Operating!F13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$47,'Assumptions'!$F$66))","Operating!F14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$48,'Assumptions'!$F$67))","Operating!F15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$49,'Assumptions'!$F$68))","Operating!F16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$50,'Assumptions'!$F$69))","Operating!F17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$51,'Assumptions'!$F$70))","Operating!F18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$52,'Assumptions'!$F$71))","Operating!F19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$53,'Assumptions'!$F$72))","Operating!F20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$F$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$F$54,'Assumptions'!$F$73))","Operating!F23":"='Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12","Operating!F24":"='Operating'!$F$10*'Operating'!$F$13","Operating!F25":"='Operating'!$F$23*'Operating'!$F$14","Operating!F26":"='Operating'!$F$23-'Operating'!$F$24-'Operating'!$F$25-'Operating'!$F$16","Operating!F27":"=MAX(0,'Operating'!$F$26)*'Operating'!$F$15","Operating!F28":"='Operating'!$F$26-'Operating'!$F$27","Operating!F29":"='Operating'!$F$28+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19","Operating!F30":"='Operating'!$F$29*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0)","Operating!F31":"='Operating'!$F$30/(1+'Operating'!$B$4)^4","Operating!F32":"='Operating'!$E$32+'Operating'!$F$30","Operating!G9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+5","Operating!G10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$44,'Assumptions'!$G$63))","Operating!G11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$45,'Assumptions'!$G$64))","Operating!G12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$46,'Assumptions'!$G$65))","Operating!G13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$47,'Assumptions'!$G$66))","Operating!G14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$48,'Assumptions'!$G$67))","Operating!G15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$49,'Assumptions'!$G$68))","Operating!G16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$50,'Assumptions'!$G$69))","Operating!G17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$51,'Assumptions'!$G$70))","Operating!G18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$52,'Assumptions'!$G$71))","Operating!G19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$53,'Assumptions'!$G$72))","Operating!G20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$G$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$G$54,'Assumptions'!$G$73))","Operating!G23":"='Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12","Operating!G24":"='Operating'!$G$10*'Operating'!$G$13","Operating!G25":"='Operating'!$G$23*'Operating'!$G$14","Operating!G26":"='Operating'!$G$23-'Operating'!$G$24-'Operating'!$G$25-'Operating'!$G$16","Operating!G27":"=MAX(0,'Operating'!$G$26)*'Operating'!$G$15","Operating!G28":"='Operating'!$G$26-'Operating'!$G$27","Operating!G29":"='Operating'!$G$28+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19","Operating!G30":"='Operating'!$G$29*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0)","Operating!G31":"='Operating'!$G$30/(1+'Operating'!$B$4)^5","Operating!G32":"='Operating'!$F$32+'Operating'!$G$30","Operating!H9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+6","Operating!H10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$44,'Assumptions'!$H$63))","Operating!H11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$45,'Assumptions'!$H$64))","Operating!H12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$46,'Assumptions'!$H$65))","Operating!H13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$47,'Assumptions'!$H$66))","Operating!H14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$48,'Assumptions'!$H$67))","Operating!H15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$49,'Assumptions'!$H$68))","Operating!H16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$50,'Assumptions'!$H$69))","Operating!H17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$51,'Assumptions'!$H$70))","Operating!H18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$52,'Assumptions'!$H$71))","Operating!H19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$53,'Assumptions'!$H$72))","Operating!H20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$H$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$H$54,'Assumptions'!$H$73))","Operating!H23":"='Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12","Operating!H24":"='Operating'!$H$10*'Operating'!$H$13","Operating!H25":"='Operating'!$H$23*'Operating'!$H$14","Operating!H26":"='Operating'!$H$23-'Operating'!$H$24-'Operating'!$H$25-'Operating'!$H$16","Operating!H27":"=MAX(0,'Operating'!$H$26)*'Operating'!$H$15","Operating!H28":"='Operating'!$H$26-'Operating'!$H$27","Operating!H29":"='Operating'!$H$28+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19","Operating!H30":"='Operating'!$H$29*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0)","Operating!H31":"='Operating'!$H$30/(1+'Operating'!$B$4)^6","Operating!H32":"='Operating'!$G$32+'Operating'!$H$30","Operating!I9":"=YEAR(DATEVALUE('Assumptions'!$B$12))+7","Operating!I10":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$25,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$44,'Assumptions'!$I$63))","Operating!I11":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$26,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$45,'Assumptions'!$I$64))","Operating!I12":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$27,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$46,'Assumptions'!$I$65))","Operating!I13":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$28,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$47,'Assumptions'!$I$66))","Operating!I14":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$29,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$48,'Assumptions'!$I$67))","Operating!I15":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$30,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$49,'Assumptions'!$I$68))","Operating!I16":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$31,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$50,'Assumptions'!$I$69))","Operating!I17":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$32,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$51,'Assumptions'!$I$70))","Operating!I18":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$33,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$52,'Assumptions'!$I$71))","Operating!I19":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$34,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$53,'Assumptions'!$I$72))","Operating!I20":"=IF(Assumptions!$B$4=\"bear\",'Assumptions'!$I$35,IF(Assumptions!$B$4=\"base\",'Assumptions'!$I$54,'Assumptions'!$I$73))","Operating!I23":"='Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12","Operating!I24":"='Operating'!$I$10*'Operating'!$I$13","Operating!I25":"='Operating'!$I$23*'Operating'!$I$14","Operating!I26":"='Operating'!$I$23-'Operating'!$I$24-'Operating'!$I$25-'Operating'!$I$16","Operating!I27":"=MAX(0,'Operating'!$I$26)*'Operating'!$I$15","Operating!I28":"='Operating'!$I$26-'Operating'!$I$27","Operating!I29":"='Operating'!$I$28+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19","Operating!I30":"='Operating'!$I$29*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0)","Operating!I31":"='Operating'!$I$30/(1+'Operating'!$B$4)^7","Operating!I32":"='Operating'!$H$32+'Operating'!$I$30","Valuation!B5":"=SUM(Operating!C31:I31)","Valuation!B6":"='Assumptions'!$B$7","Valuation!B7":"='Assumptions'!$B$9","Valuation!B8":"='Assumptions'!$B$8","Valuation!B9":"=B5+B6+B7-B8","Valuation!B10":"='Assumptions'!$B$10","Valuation!B11":"=B9/B10","Valuation!B12":"=MIN('Assumptions'!$B$7,Operating!C32:I32)","Valuation!B15":"=IF('Assumptions'!$B$11=\"\",\"Unavailable\",'Assumptions'!$B$11)","Valuation!B16":"=IF(AND(ISNUMBER(B15),B15&gt;0),B11/B15-1,\"Unavailable\")","Sensitivities!C7":"=MAX(0,'Operating'!$B$4+(-0.02))","Sensitivities!D7":"=MAX(0,'Operating'!$B$4+(0))","Sensitivities!E7":"=MAX(0,'Operating'!$B$4+(0.02))","Sensitivities!C17":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^1","Sensitivities!D17":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^2","Sensitivities!E17":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^3","Sensitivities!F17":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^4","Sensitivities!G17":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^5","Sensitivities!H17":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^6","Sensitivities!I17":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^7","Sensitivities!C8":"=(SUM(C17:I17)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C18":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^1","Sensitivities!D18":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^2","Sensitivities!E18":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^3","Sensitivities!F18":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^4","Sensitivities!G18":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^5","Sensitivities!H18":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^6","Sensitivities!I18":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^7","Sensitivities!D8":"=(SUM(C18:I18)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C19":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$8)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^1","Sensitivities!D19":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$8)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^2","Sensitivities!E19":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$8)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^3","Sensitivities!F19":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$8)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^4","Sensitivities!G19":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$8)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^5","Sensitivities!H19":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$8)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^6","Sensitivities!I19":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$8)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^7","Sensitivities!E8":"=(SUM(C19:I19)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C20":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^1","Sensitivities!D20":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^2","Sensitivities!E20":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^3","Sensitivities!F20":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^4","Sensitivities!G20":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^5","Sensitivities!H20":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^6","Sensitivities!I20":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^7","Sensitivities!C9":"=(SUM(C20:I20)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C21":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^1","Sensitivities!D21":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^2","Sensitivities!E21":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^3","Sensitivities!F21":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Op</t>
+  </si>
+  <si>
+    <t xml:space="preserve">erating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^4","Sensitivities!G21":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^5","Sensitivities!H21":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^6","Sensitivities!I21":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^7","Sensitivities!D9":"=(SUM(C21:I21)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C22":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$9)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^1","Sensitivities!D22":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$9)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^2","Sensitivities!E22":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$9)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^3","Sensitivities!F22":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$9)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^4","Sensitivities!G22":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$9)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^5","Sensitivities!H22":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$9)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^6","Sensitivities!I22":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$9)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^7","Sensitivities!E9":"=(SUM(C22:I22)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C23":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^1","Sensitivities!D23":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^2","Sensitivities!E23":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^3","Sensitivities!F23":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^4","Sensitivities!G23":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^5","Sensitivities!H23":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^6","Sensitivities!I23":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+C7)^7","Sensitivities!C10":"=(SUM(C23:I23)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C24":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^1","Sensitivities!D24":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^2","Sensitivities!E24":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^3","Sensitivities!F24":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^4","Sensitivities!G24":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^5","Sensitivities!H24":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^6","Sensitivities!I24":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+D7)^7","Sensitivities!D10":"=(SUM(C24:I24)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Sensitivities!C25":"=((((('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16)-MAX(0,(('Operating'!$C$10*'Operating'!$C$11*'Operating'!$C$12*$B$10)*(1-'Operating'!$C$14)-'Operating'!$C$10*'Operating'!$C$13-'Operating'!$C$16))*'Operating'!$C$15)+'Operating'!$C$16-'Operating'!$C$17-'Operating'!$C$18-'Operating'!$C$19)*'Operating'!$B$5-'Operating'!$C$20+IF(1='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^1","Sensitivities!D25":"=((((('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16)-MAX(0,(('Operating'!$D$10*'Operating'!$D$11*'Operating'!$D$12*$B$10)*(1-'Operating'!$D$14)-'Operating'!$D$10*'Operating'!$D$13-'Operating'!$D$16))*'Operating'!$D$15)+'Operating'!$D$16-'Operating'!$D$17-'Operating'!$D$18-'Operating'!$D$19)*'Operating'!$B$5-'Operating'!$D$20+IF(2='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^2","Sensitivities!E25":"=((((('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16)-MAX(0,(('Operating'!$E$10*'Operating'!$E$11*'Operating'!$E$12*$B$10)*(1-'Operating'!$E$14)-'Operating'!$E$10*'Operating'!$E$13-'Operating'!$E$16))*'Operating'!$E$15)+'Operating'!$E$16-'Operating'!$E$17-'Operating'!$E$18-'Operating'!$E$19)*'Operating'!$B$5-'Operating'!$E$20+IF(3='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^3","Sensitivities!F25":"=((((('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16)-MAX(0,(('Operating'!$F$10*'Operating'!$F$11*'Operating'!$F$12*$B$10)*(1-'Operating'!$F$14)-'Operating'!$F$10*'Operating'!$F$13-'Operating'!$F$16))*'Operating'!$F$15)+'Operating'!$F$16-'Operating'!$F$17-'Operating'!$F$18-'Operating'!$F$19)*'Operating'!$B$5-'Operating'!$F$20+IF(4='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^4","Sensitivities!G25":"=((((('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16)-MAX(0,(('Operating'!$G$10*'Operating'!$G$11*'Operating'!$G$12*$B$10)*(1-'Operating'!$G$14)-'Operating'!$G$10*'Operating'!$G$13-'Operating'!$G$16))*'Operating'!$G$15)+'Operating'!$G$16-'Operating'!$G$17-'Operating'!$G$18-'Operating'!$G$19)*'Operating'!$B$5-'Operating'!$G$20+IF(5='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^5","Sensitivities!H25":"=((((('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16)-MAX(0,(('Operating'!$H$10*'Operating'!$H$11*'Operating'!$H$12*$B$10)*(1-'Operating'!$H$14)-'Operating'!$H$10*'Operating'!$H$13-'Operating'!$H$16))*'Operating'!$H$15)+'Operating'!$H$16-'Operating'!$H$17-'Operating'!$H$18-'Operating'!$H$19)*'Operating'!$B$5-'Operating'!$H$20+IF(6='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^6","Sensitivities!I25":"=((((('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16)-MAX(0,(('Operating'!$I$10*'Operating'!$I$11*'Operating'!$I$12*$B$10)*(1-'Operating'!$I$14)-'Operating'!$I$10*'Operating'!$I$13-'Operating'!$I$16))*'Operating'!$I$15)+'Operating'!$I$16-'Operating'!$I$17-'Operating'!$I$18-'Operating'!$I$19)*'Operating'!$B$5-'Operating'!$I$20+IF(7='Operating'!$B$7,'Operating'!$B$6,0))/(1+E7)^7","Sensitivities!E10":"=(SUM(C25:I25)+'Assumptions'!$B$7+'Assumptions'!$B$9-'Assumptions'!$B$8)/'Assumptions'!$B$10","Checks!B5":"=IF(OR(Assumptions!B4=\"bear\",Assumptions!B4=\"base\",Assumptions!B4=\"bull\"),\"PASS\",\"FAIL\")","Checks!B6":"=IF('Assumptions'!$B$10&gt;0,\"PASS\",\"FAIL\")","Checks!B7":"=IF(ABS(Valuation!B9-(Valuation!B5+Valuation!B6+Valuation!B7-Valuation!B8))&lt;0.01,\"PASS\",\"FAIL\")","Checks!B8":"=IF(ABS(Sensitivities!D9-Valuation!B11)&lt;0.000001,\"PASS\",\"FAIL\")","Checks!B9":"=IF(OR(AND('Assumptions'!$B$11=\"\",'Assumptions'!$B$13=\"\"),AND(ISNUMBER('Assumptions'!$B$11),'Assumptions'!$B$11&gt;0,'Assumptions'!$B$13&lt;&gt;\"\")),\"PASS\",\"FAIL\")","Checks!B10":"=IF(AND('Operating'!$B$5&gt;=0,'Operating'!$B$5&lt;=1),\"PASS\",\"FAIL\")","Summary!B7":"=Assumptions!B4","Summary!B8":"='Valuation'!$B$11","Summary!B9":"='Valuation'!$B$9","Summary!B10":"='Valuation'!$B$12"}}</t>
   </si>
 </sst>
 </file>
@@ -7059,7 +7057,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7082,7 +7080,7 @@
       <b val="true"/>
       <sz val="21"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7090,7 +7088,7 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7098,21 +7096,21 @@
       <b val="true"/>
       <sz val="15"/>
       <color rgb="FF008000"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF243746"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF667085"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7139,7 +7137,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7147,7 +7145,7 @@
       <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7159,7 +7157,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF202020"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7174,7 +7172,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7182,7 +7180,7 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF202020"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -7278,20 +7276,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -7302,52 +7300,52 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="169" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="168" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7665,11 +7663,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="16272943"/>
-        <c:axId val="69783871"/>
+        <c:axId val="62413779"/>
+        <c:axId val="86722974"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="16272943"/>
+        <c:axId val="62413779"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7702,7 +7700,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69783871"/>
+        <c:crossAx val="86722974"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7710,7 +7708,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69783871"/>
+        <c:axId val="86722974"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7786,7 +7784,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16272943"/>
+        <c:crossAx val="62413779"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7986,11 +7984,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="52017761"/>
-        <c:axId val="70453521"/>
+        <c:axId val="22913737"/>
+        <c:axId val="1845878"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52017761"/>
+        <c:axId val="22913737"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8023,7 +8021,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70453521"/>
+        <c:crossAx val="1845878"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8031,7 +8029,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70453521"/>
+        <c:axId val="1845878"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8107,7 +8105,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52017761"/>
+        <c:crossAx val="22913737"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8579,14 +8577,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>514080</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>285120</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>885600</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>47160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -8594,8 +8592,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="6000840"/>
-        <a:ext cx="5407560" cy="2856960"/>
+        <a:off x="0" y="4857840"/>
+        <a:ext cx="3729600" cy="2333160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8607,16 +8605,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>418680</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>285120</xdr:rowOff>
+      <xdr:colOff>428400</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>47160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -8624,8 +8622,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7390080" y="6000840"/>
-        <a:ext cx="5412240" cy="2856960"/>
+        <a:off x="5123880" y="4857840"/>
+        <a:ext cx="3803400" cy="2333160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8824,11 +8822,11 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8925,7 +8923,7 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -8935,7 +8933,7 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -8957,7 +8955,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -8967,7 +8965,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -8977,7 +8975,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -8995,7 +8993,7 @@
     <mergeCell ref="A16:H19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -9012,11 +9010,11 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I73"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9044,10 +9042,10 @@
       <c r="I2" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -9060,75 +9058,75 @@
       <c r="H4" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="10" t="n">
         <v>374000000</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="10" t="n">
         <v>3285000</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="10" t="n">
         <v>886391538</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9168,31 +9166,31 @@
       <c r="I19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="12" t="n">
         <v>0.12</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="0" t="n">
@@ -9200,344 +9198,344 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="13" t="n">
         <v>2027</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D24" s="13" t="n">
         <v>2028</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="13" t="n">
         <v>2029</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="13" t="n">
         <v>2030</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="13" t="n">
         <v>2031</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="H24" s="13" t="n">
         <v>2032</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="I24" s="13" t="n">
         <v>2033</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="10" t="n">
         <v>10158.3</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="10" t="n">
         <v>10158.3</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="10" t="n">
         <v>10158.3</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="10" t="n">
+      <c r="F25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="10" t="n">
         <v>51008</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="10" t="n">
         <v>51008</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="10" t="n">
         <v>51008</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="10" t="n">
+      <c r="F26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="10" t="n">
+      <c r="F27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="10" t="n">
         <v>30181.8</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="10" t="n">
         <v>30181.8</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="10" t="n">
         <v>30181.8</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="10" t="n">
+      <c r="F28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="10" t="n">
+      <c r="C29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="10" t="n">
+      <c r="F30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="10" t="n">
+      <c r="B31" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="9" t="n">
+      <c r="B32" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="10" t="n">
+      <c r="F32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="10" t="n">
+      <c r="B33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="9" t="n">
+      <c r="B34" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10" t="n">
         <v>100000000</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="10" t="n">
+      <c r="F34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="9" t="n">
+      <c r="B35" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="10" t="n">
+      <c r="F35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9555,31 +9553,31 @@
       <c r="I38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="12" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B40" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B41" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B42" s="0" t="n">
@@ -9587,344 +9585,344 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="13" t="n">
         <v>2027</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D43" s="13" t="n">
         <v>2028</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="13" t="n">
         <v>2029</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F43" s="13" t="n">
         <v>2030</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G43" s="13" t="n">
         <v>2031</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="H43" s="13" t="n">
         <v>2032</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="I43" s="13" t="n">
         <v>2033</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="10" t="n">
         <v>11287</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="10" t="n">
         <v>11287</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="10" t="n">
         <v>11287</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>11287</v>
       </c>
-      <c r="G44" s="9" t="n">
+      <c r="G44" s="10" t="n">
         <v>11287</v>
       </c>
-      <c r="H44" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="10" t="n">
+      <c r="H44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="10" t="n">
         <v>63760</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D45" s="10" t="n">
         <v>63760</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="10" t="n">
         <v>63760</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="10" t="n">
         <v>63760</v>
       </c>
-      <c r="G45" s="9" t="n">
+      <c r="G45" s="10" t="n">
         <v>63760</v>
       </c>
-      <c r="H45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="10" t="n">
+      <c r="H45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="10" t="n">
+      <c r="H46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="10" t="n">
         <v>27438</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D47" s="10" t="n">
         <v>27438</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="10" t="n">
         <v>27438</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="10" t="n">
         <v>27438</v>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="G47" s="10" t="n">
         <v>27438</v>
       </c>
-      <c r="H47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="10" t="n">
+      <c r="H47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="10" t="n">
+      <c r="C48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="11" t="n">
+      <c r="C49" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E49" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="F49" s="11" t="n">
+      <c r="F49" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="G49" s="11" t="n">
+      <c r="G49" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="H49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="10" t="n">
+      <c r="H49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="10" t="n">
+      <c r="B50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="9" t="n">
+      <c r="B51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D51" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="G51" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="H51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="10" t="n">
+      <c r="H51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="10" t="n">
+      <c r="B52" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B53" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="9" t="n">
+      <c r="B53" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="10" t="n">
         <v>100000000</v>
       </c>
-      <c r="H53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="10" t="n">
+      <c r="H53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="9" t="n">
+      <c r="B54" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="D54" s="9" t="n">
+      <c r="D54" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="E54" s="9" t="n">
+      <c r="E54" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="F54" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="G54" s="9" t="n">
+      <c r="G54" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="H54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="10" t="n">
+      <c r="H54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9942,31 +9940,31 @@
       <c r="I57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B58" s="11" t="n">
+      <c r="B58" s="12" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B59" s="11" t="n">
+      <c r="B59" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="9" t="n">
+      <c r="B60" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B61" s="0" t="n">
@@ -9974,344 +9972,344 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C62" s="12" t="n">
+      <c r="C62" s="13" t="n">
         <v>2027</v>
       </c>
-      <c r="D62" s="12" t="n">
+      <c r="D62" s="13" t="n">
         <v>2028</v>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="E62" s="13" t="n">
         <v>2029</v>
       </c>
-      <c r="F62" s="12" t="n">
+      <c r="F62" s="13" t="n">
         <v>2030</v>
       </c>
-      <c r="G62" s="12" t="n">
+      <c r="G62" s="13" t="n">
         <v>2031</v>
       </c>
-      <c r="H62" s="12" t="n">
+      <c r="H62" s="13" t="n">
         <v>2032</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="I62" s="13" t="n">
         <v>2033</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C63" s="9" t="n">
+      <c r="C63" s="10" t="n">
         <v>12415.7</v>
       </c>
-      <c r="D63" s="9" t="n">
+      <c r="D63" s="10" t="n">
         <v>12415.7</v>
       </c>
-      <c r="E63" s="9" t="n">
+      <c r="E63" s="10" t="n">
         <v>12415.7</v>
       </c>
-      <c r="F63" s="9" t="n">
+      <c r="F63" s="10" t="n">
         <v>12415.7</v>
       </c>
-      <c r="G63" s="9" t="n">
+      <c r="G63" s="10" t="n">
         <v>12415.7</v>
       </c>
-      <c r="H63" s="9" t="n">
+      <c r="H63" s="10" t="n">
         <v>12415.7</v>
       </c>
-      <c r="I63" s="9" t="n">
+      <c r="I63" s="10" t="n">
         <v>12415.7</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="9" t="n">
+      <c r="C64" s="10" t="n">
         <v>76512</v>
       </c>
-      <c r="D64" s="9" t="n">
+      <c r="D64" s="10" t="n">
         <v>76512</v>
       </c>
-      <c r="E64" s="9" t="n">
+      <c r="E64" s="10" t="n">
         <v>76512</v>
       </c>
-      <c r="F64" s="9" t="n">
+      <c r="F64" s="10" t="n">
         <v>76512</v>
       </c>
-      <c r="G64" s="9" t="n">
+      <c r="G64" s="10" t="n">
         <v>76512</v>
       </c>
-      <c r="H64" s="9" t="n">
+      <c r="H64" s="10" t="n">
         <v>76512</v>
       </c>
-      <c r="I64" s="9" t="n">
+      <c r="I64" s="10" t="n">
         <v>76512</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="C65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="9" t="n">
+      <c r="D65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="9" t="n">
+      <c r="E65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="9" t="n">
+      <c r="F65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G65" s="9" t="n">
+      <c r="G65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H65" s="9" t="n">
+      <c r="H65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I65" s="9" t="n">
+      <c r="I65" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C66" s="9" t="n">
+      <c r="C66" s="10" t="n">
         <v>26066.1</v>
       </c>
-      <c r="D66" s="9" t="n">
+      <c r="D66" s="10" t="n">
         <v>26066.1</v>
       </c>
-      <c r="E66" s="9" t="n">
+      <c r="E66" s="10" t="n">
         <v>26066.1</v>
       </c>
-      <c r="F66" s="9" t="n">
+      <c r="F66" s="10" t="n">
         <v>26066.1</v>
       </c>
-      <c r="G66" s="9" t="n">
+      <c r="G66" s="10" t="n">
         <v>26066.1</v>
       </c>
-      <c r="H66" s="9" t="n">
+      <c r="H66" s="10" t="n">
         <v>26066.1</v>
       </c>
-      <c r="I66" s="9" t="n">
+      <c r="I66" s="10" t="n">
         <v>26066.1</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="11" t="n">
+      <c r="C67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C68" s="11" t="n">
+      <c r="C68" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="D68" s="11" t="n">
+      <c r="D68" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E68" s="11" t="n">
+      <c r="E68" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="F68" s="11" t="n">
+      <c r="F68" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="G68" s="11" t="n">
+      <c r="G68" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="H68" s="11" t="n">
+      <c r="H68" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="I68" s="11" t="n">
+      <c r="I68" s="12" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="9" t="n">
+      <c r="B69" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="9" t="n">
+      <c r="B70" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="D70" s="9" t="n">
+      <c r="D70" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="E70" s="9" t="n">
+      <c r="E70" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="F70" s="9" t="n">
+      <c r="F70" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="G70" s="9" t="n">
+      <c r="G70" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="H70" s="9" t="n">
+      <c r="H70" s="10" t="n">
         <v>93600000</v>
       </c>
-      <c r="I70" s="9" t="n">
+      <c r="I70" s="10" t="n">
         <v>93600000</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="9" t="n">
+      <c r="B71" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="9" t="n">
+      <c r="B72" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="10" t="n">
         <v>100000000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" s="9" t="n">
+      <c r="B73" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="D73" s="9" t="n">
+      <c r="D73" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="E73" s="9" t="n">
+      <c r="E73" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="F73" s="9" t="n">
+      <c r="F73" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="G73" s="9" t="n">
+      <c r="G73" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="H73" s="9" t="n">
+      <c r="H73" s="10" t="n">
         <v>2240000</v>
       </c>
-      <c r="I73" s="9" t="n">
+      <c r="I73" s="10" t="n">
         <v>2240000</v>
       </c>
     </row>
@@ -10331,13 +10329,14 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter>&amp;Lasx-mlx | Assumptions&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
-  <rowBreaks count="2" manualBreakCount="2">
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="18" man="true" max="16383" min="0"/>
     <brk id="37" man="true" max="16383" min="0"/>
     <brk id="56" man="true" max="16383" min="0"/>
   </rowBreaks>
@@ -10352,15 +10351,15 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I79"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10401,2138 +10400,2138 @@
       <c r="I4" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>293606000</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="13" t="s">
+      <c r="D7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>2849000</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="D8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>436000</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="D9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>886391538</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>33035000</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="13" t="s">
+      <c r="D11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="7" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>128323000</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="D12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>13747000</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="13" t="s">
+      <c r="D13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>22211000</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="13" t="s">
+      <c r="D14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C15" s="14" t="n">
         <v>10748</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="7" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13" t="s">
+      <c r="E16" s="7"/>
+      <c r="F16" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>2809</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13" t="s">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C18" s="14" t="n">
         <v>11287</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13" t="s">
+      <c r="E18" s="7"/>
+      <c r="F18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>73834</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="13" t="s">
+      <c r="E19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C20" s="14" t="n">
         <v>63760</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="13" t="s">
+      <c r="E20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>20251</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="13" t="s">
+      <c r="E21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="I21" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>19349</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="13" t="s">
+      <c r="E22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="I22" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C23" s="14" t="n">
         <v>8758</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="13" t="s">
+      <c r="E23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>34865</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="13" t="s">
+      <c r="E24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C25" s="14" t="n">
         <v>23400000</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="13" t="s">
+      <c r="D25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="7" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>16450000</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="13" t="s">
+      <c r="D26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="7" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C27" s="14" t="n">
         <v>6950000</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="13" t="s">
+      <c r="D27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I27" s="13" t="s">
+      <c r="I27" s="7" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="14" t="n">
         <v>374000000</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="13" t="s">
+      <c r="D28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="7" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C29" s="14" t="n">
         <v>560000</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="13" t="s">
+      <c r="D29" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="13" t="s">
+      <c r="I29" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="14" t="n">
         <v>284999000</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="13" t="s">
+      <c r="D30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="I30" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>218820000</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="13" t="s">
+      <c r="D31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I31" s="13" t="s">
+      <c r="I31" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>158275000</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="13" t="s">
+      <c r="D32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I32" s="13" t="s">
+      <c r="I32" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>123558000</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="13" t="s">
+      <c r="D33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H33" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I33" s="13" t="s">
+      <c r="I33" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>126724000</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="13" t="s">
+      <c r="D34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="I34" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C35" s="14" t="n">
         <v>95262000</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="13" t="s">
+      <c r="D35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I35" s="13" t="s">
+      <c r="I35" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C36" s="14" t="n">
         <v>4212000</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="13" t="s">
+      <c r="D36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H36" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I36" s="13" t="s">
+      <c r="I36" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C37" s="14" t="n">
         <v>2744000</v>
       </c>
-      <c r="D37" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="13" t="s">
+      <c r="D37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C38" s="14" t="n">
         <v>980000</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="13" t="s">
+      <c r="D38" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="14" t="n">
         <v>566000</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="13" t="s">
+      <c r="D39" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H39" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I39" s="13" t="s">
+      <c r="I39" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="14" t="n">
         <v>138275000</v>
       </c>
-      <c r="D40" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" s="13" t="s">
+      <c r="D40" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H40" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="I40" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="14" t="n">
         <v>120227000</v>
       </c>
-      <c r="D41" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F41" s="13" t="s">
+      <c r="D41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I41" s="13" t="s">
+      <c r="I41" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C42" s="14" t="n">
         <v>33670000</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="13" t="s">
+      <c r="D42" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G42" s="13" t="s">
+      <c r="G42" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H42" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I42" s="13" t="s">
+      <c r="I42" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="14" t="n">
         <v>17878000</v>
       </c>
-      <c r="D43" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="13" t="s">
+      <c r="D43" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H43" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I43" s="13" t="s">
+      <c r="I43" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C44" s="14" t="n">
         <v>104605000</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="13" t="s">
+      <c r="D44" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I44" s="13" t="s">
+      <c r="I44" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="14" t="n">
         <v>102349000</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="13" t="s">
+      <c r="D45" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="G45" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I45" s="13" t="s">
+      <c r="I45" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C46" s="14" t="n">
         <v>220644000</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="13" t="s">
+      <c r="D46" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="G46" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H46" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I46" s="13" t="s">
+      <c r="I46" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C47" s="14" t="n">
         <v>36473000</v>
       </c>
-      <c r="D47" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" s="13" t="s">
+      <c r="D47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G47" s="13" t="s">
+      <c r="G47" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H47" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I47" s="13" t="s">
+      <c r="I47" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C48" s="14" t="n">
         <v>8666000</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="13" t="s">
+      <c r="D48" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G48" s="13" t="s">
+      <c r="G48" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H48" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I48" s="13" t="s">
+      <c r="I48" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C49" s="14" t="n">
         <v>29488000</v>
       </c>
-      <c r="D49" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="13" t="s">
+      <c r="D49" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G49" s="13" t="s">
+      <c r="G49" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H49" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I49" s="13" t="s">
+      <c r="I49" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C50" s="14" t="n">
         <v>37573000</v>
       </c>
-      <c r="D50" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="13" t="s">
+      <c r="D50" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="G50" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H50" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I50" s="13" t="s">
+      <c r="I50" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="14" t="n">
         <v>363459000</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="13" t="s">
+      <c r="D51" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G51" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H51" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I51" s="13" t="s">
+      <c r="I51" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C52" s="14" t="n">
         <v>271243000</v>
       </c>
-      <c r="D52" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="13" t="s">
+      <c r="D52" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H52" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I52" s="13" t="s">
+      <c r="I52" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="14" t="n">
         <v>255050000</v>
       </c>
-      <c r="D53" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="13" t="s">
+      <c r="D53" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G53" s="13" t="s">
+      <c r="G53" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H53" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I53" s="13" t="s">
+      <c r="I53" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C54" s="14" t="n">
         <v>233789000</v>
       </c>
-      <c r="D54" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="13" t="s">
+      <c r="D54" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G54" s="13" t="s">
+      <c r="G54" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H54" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I54" s="13" t="s">
+      <c r="I54" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C55" s="14" t="n">
         <v>618509000</v>
       </c>
-      <c r="D55" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="13" t="s">
+      <c r="D55" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="G55" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H55" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I55" s="13" t="s">
+      <c r="I55" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C56" s="14" t="n">
         <v>505032000</v>
       </c>
-      <c r="D56" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="13" t="s">
+      <c r="D56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="G56" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H56" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I56" s="13" t="s">
+      <c r="I56" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C57" s="14" t="n">
         <v>17091000</v>
       </c>
-      <c r="D57" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" s="13" t="s">
+      <c r="D57" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H57" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I57" s="13" t="s">
+      <c r="I57" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C58" s="14" t="n">
         <v>20972000</v>
       </c>
-      <c r="D58" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="13" t="s">
+      <c r="D58" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G58" s="13" t="s">
+      <c r="G58" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I58" s="13" t="s">
+      <c r="I58" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C59" s="14" t="n">
         <v>3645000</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F59" s="13" t="s">
+      <c r="D59" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G59" s="13" t="s">
+      <c r="G59" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H59" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I59" s="13" t="s">
+      <c r="I59" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="14" t="n">
         <v>2508000</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="13" t="s">
+      <c r="D60" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G60" s="13" t="s">
+      <c r="G60" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H60" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I60" s="13" t="s">
+      <c r="I60" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C61" s="14" t="n">
         <v>51679000</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="13" t="s">
+      <c r="D61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G61" s="13" t="s">
+      <c r="G61" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H61" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I61" s="13" t="s">
+      <c r="I61" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C62" s="14" t="n">
         <v>43857000</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="13" t="s">
+      <c r="D62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G62" s="13" t="s">
+      <c r="G62" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I62" s="13" t="s">
+      <c r="I62" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C63" s="14" t="n">
         <v>34297000</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="13" t="s">
+      <c r="D63" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G63" s="13" t="s">
+      <c r="G63" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H63" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I63" s="13" t="s">
+      <c r="I63" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C64" s="14" t="n">
         <v>33401000</v>
       </c>
-      <c r="D64" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="13" t="s">
+      <c r="D64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G64" s="13" t="s">
+      <c r="G64" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H64" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I64" s="13" t="s">
+      <c r="I64" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C65" s="14" t="n">
         <v>85976000</v>
       </c>
-      <c r="D65" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="13" t="s">
+      <c r="D65" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G65" s="13" t="s">
+      <c r="G65" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H65" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I65" s="13" t="s">
+      <c r="I65" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C66" s="14" t="n">
         <v>77258000</v>
       </c>
-      <c r="D66" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" s="13" t="s">
+      <c r="D66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G66" s="13" t="s">
+      <c r="G66" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H66" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I66" s="13" t="s">
+      <c r="I66" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C67" s="14" t="n">
         <v>532533000</v>
       </c>
-      <c r="D67" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="13" t="s">
+      <c r="D67" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G67" s="13" t="s">
+      <c r="G67" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H67" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I67" s="13" t="s">
+      <c r="I67" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C68" s="14" t="n">
         <v>427774000</v>
       </c>
-      <c r="D68" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="13" t="s">
+      <c r="D68" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G68" s="13" t="s">
+      <c r="G68" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H68" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I68" s="13" t="s">
+      <c r="I68" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C69" s="14" t="n">
         <v>143567000</v>
       </c>
-      <c r="D69" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" s="13" t="s">
+      <c r="D69" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G69" s="13" t="s">
+      <c r="G69" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H69" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I69" s="13" t="s">
+      <c r="I69" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C70" s="14" t="n">
         <v>17425000</v>
       </c>
-      <c r="D70" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="13" t="s">
+      <c r="D70" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G70" s="13" t="s">
+      <c r="G70" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H70" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I70" s="13" t="s">
+      <c r="I70" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C71" s="14" t="n">
         <v>22511000</v>
       </c>
-      <c r="D71" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F71" s="13" t="s">
+      <c r="D71" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G71" s="13" t="s">
+      <c r="G71" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H71" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I71" s="13" t="s">
+      <c r="I71" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C72" s="14" t="n">
         <v>-52493000</v>
       </c>
-      <c r="D72" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" s="13" t="s">
+      <c r="D72" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G72" s="13" t="s">
+      <c r="G72" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H72" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I72" s="13" t="s">
+      <c r="I72" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C73" s="14" t="n">
         <v>-55453000</v>
       </c>
-      <c r="D73" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="13" t="s">
+      <c r="D73" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G73" s="13" t="s">
+      <c r="G73" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H73" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I73" s="13" t="s">
+      <c r="I73" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C74" s="14" t="n">
         <v>-2868000</v>
       </c>
-      <c r="D74" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="13" t="s">
+      <c r="D74" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G74" s="13" t="s">
+      <c r="G74" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H74" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I74" s="13" t="s">
+      <c r="I74" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C75" s="14" t="n">
         <v>-10512000</v>
       </c>
-      <c r="D75" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="13" t="s">
+      <c r="D75" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G75" s="13" t="s">
+      <c r="G75" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H75" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I75" s="13" t="s">
+      <c r="I75" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C76" s="14" t="n">
         <v>72962000</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" s="13" t="s">
+      <c r="D76" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G76" s="13" t="s">
+      <c r="G76" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H76" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I76" s="13" t="s">
+      <c r="I76" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C77" s="14" t="n">
         <v>77602000</v>
       </c>
-      <c r="D77" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77" s="13" t="s">
+      <c r="D77" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G77" s="13" t="s">
+      <c r="G77" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H77" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I77" s="13" t="s">
+      <c r="I77" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C78" s="14" t="n">
         <v>220644000</v>
       </c>
-      <c r="D78" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="13" t="s">
+      <c r="D78" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G78" s="13" t="s">
+      <c r="G78" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H78" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I78" s="13" t="s">
+      <c r="I78" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C79" s="14" t="n">
         <v>143042000</v>
       </c>
-      <c r="D79" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="13" t="s">
+      <c r="D79" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G79" s="13" t="s">
+      <c r="G79" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H79" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I79" s="13" t="s">
+      <c r="I79" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -12618,7 +12617,7 @@
     <hyperlink ref="H79" r:id="rId73" location="page=26" display="Open source report"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -12635,11 +12634,11 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12667,7 +12666,7 @@
       <c r="I2" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="16" t="n">
@@ -12676,7 +12675,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="16" t="n">
@@ -12685,7 +12684,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="17" t="n">
@@ -12694,7 +12693,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B7" s="17" t="n">
@@ -12703,7 +12702,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="7" t="s">
         <v>122</v>
       </c>
       <c r="B8" s="17" t="str">
@@ -12712,43 +12711,43 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="13" t="n">
         <f aca="false">YEAR(DATEVALUE(Assumptions!$B$12))+1</f>
         <v>2027</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <f aca="false">YEAR(DATEVALUE(Assumptions!$B$12))+2</f>
         <v>2028</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <f aca="false">YEAR(DATEVALUE(Assumptions!$B$12))+3</f>
         <v>2029</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="13" t="n">
         <f aca="false">YEAR(DATEVALUE(Assumptions!$B$12))+4</f>
         <v>2030</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="13" t="n">
         <f aca="false">YEAR(DATEVALUE(Assumptions!$B$12))+5</f>
         <v>2031</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="13" t="n">
         <f aca="false">YEAR(DATEVALUE(Assumptions!$B$12))+6</f>
         <v>2032</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="13" t="n">
         <f aca="false">YEAR(DATEVALUE(Assumptions!$B$12))+7</f>
         <v>2033</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="17" t="n">
@@ -12781,10 +12780,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>125</v>
       </c>
       <c r="C11" s="17" t="n">
@@ -12817,10 +12816,10 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>125</v>
       </c>
       <c r="C12" s="17" t="n">
@@ -12853,10 +12852,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="17" t="n">
@@ -12889,82 +12888,82 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$C$29,IF(Assumptions!$B$4="base",Assumptions!$C$48,Assumptions!$C$67))</f>
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$D$29,IF(Assumptions!$B$4="base",Assumptions!$D$48,Assumptions!$D$67))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$E$29,IF(Assumptions!$B$4="base",Assumptions!$E$48,Assumptions!$E$67))</f>
         <v>0</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$F$29,IF(Assumptions!$B$4="base",Assumptions!$F$48,Assumptions!$F$67))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$G$29,IF(Assumptions!$B$4="base",Assumptions!$G$48,Assumptions!$G$67))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$H$29,IF(Assumptions!$B$4="base",Assumptions!$H$48,Assumptions!$H$67))</f>
         <v>0</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I14" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$I$29,IF(Assumptions!$B$4="base",Assumptions!$I$48,Assumptions!$I$67))</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$C$30,IF(Assumptions!$B$4="base",Assumptions!$C$49,Assumptions!$C$68))</f>
         <v>0.3</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$D$30,IF(Assumptions!$B$4="base",Assumptions!$D$49,Assumptions!$D$68))</f>
         <v>0.3</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$E$30,IF(Assumptions!$B$4="base",Assumptions!$E$49,Assumptions!$E$68))</f>
         <v>0.3</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$F$30,IF(Assumptions!$B$4="base",Assumptions!$F$49,Assumptions!$F$68))</f>
         <v>0.3</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$G$30,IF(Assumptions!$B$4="base",Assumptions!$G$49,Assumptions!$G$68))</f>
         <v>0.3</v>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$H$30,IF(Assumptions!$B$4="base",Assumptions!$H$49,Assumptions!$H$68))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I15" s="16" t="n">
         <f aca="false">IF(Assumptions!$B$4="bear",Assumptions!$I$30,IF(Assumptions!$B$4="base",Assumptions!$I$49,Assumptions!$I$68))</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="17" t="n">
@@ -12997,10 +12996,10 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="17" t="n">
@@ -13033,10 +13032,10 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="17" t="n">
@@ -13069,10 +13068,10 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="17" t="n">
@@ -13105,10 +13104,10 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="17" t="n">
@@ -13141,10 +13140,10 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="10" t="s">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="14" t="n">
@@ -13177,10 +13176,10 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B24" s="10" t="s">
+      <c r="A24" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="14" t="n">
@@ -13213,10 +13212,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="10" t="s">
+      <c r="A25" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="14" t="n">
@@ -13249,10 +13248,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="10" t="s">
+      <c r="A26" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="14" t="n">
@@ -13285,10 +13284,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="10" t="s">
+      <c r="A27" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="14" t="n">
@@ -13321,10 +13320,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B28" s="10" t="s">
+      <c r="A28" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="14" t="n">
@@ -13357,10 +13356,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B29" s="10" t="s">
+      <c r="A29" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="14" t="n">
@@ -13393,10 +13392,10 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="10" t="s">
+      <c r="A30" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="18" t="n">
@@ -13429,10 +13428,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B31" s="10" t="s">
+      <c r="A31" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="18" t="n">
@@ -13465,10 +13464,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B32" s="10" t="s">
+      <c r="A32" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="18" t="n">
@@ -13502,7 +13501,7 @@
     </row>
     <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -13530,7 +13529,7 @@
     <mergeCell ref="A34:I35"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -13546,16 +13545,16 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13578,104 +13577,104 @@
       <c r="I2" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>138</v>
+      <c r="A5" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">SUM(Operating!C31:I31)</f>
         <v>326987091.007811</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>374000000</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Assumptions!$B$9</f>
         <v>0</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Assumptions!$B$8</f>
         <v>3285000</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>139</v>
+      <c r="A9" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">B5+B6+B7-B8</f>
         <v>697702091.007811</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Assumptions!$B$10</f>
         <v>886391538</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>140</v>
+      <c r="A11" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="B11" s="3" t="n">
         <f aca="false">B9/B10</f>
         <v>0.787126299267323</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>141</v>
+      <c r="A12" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">MIN(Assumptions!$B$7,Operating!C32:I32)</f>
         <v>374000000</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>142</v>
+      <c r="A15" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="B15" s="17" t="str">
         <f aca="false">IF(Assumptions!$B$11="","Unavailable",Assumptions!$B$11)</f>
@@ -13683,8 +13682,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>143</v>
+      <c r="A16" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="B16" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(B15),B15&gt;0),B11/B15-1,"Unavailable")</f>
@@ -13693,7 +13692,7 @@
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -13723,7 +13722,7 @@
     <mergeCell ref="A19:F21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -13739,16 +13738,16 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13772,7 +13771,7 @@
     </row>
     <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -13854,13 +13853,13 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$8)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$8)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+C7)^1</f>
@@ -13892,8 +13891,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>149</v>
+      <c r="A18" s="11" t="s">
+        <v>148</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$8)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$8)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+D7)^1</f>
@@ -13925,8 +13924,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>150</v>
+      <c r="A19" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$8)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$8)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+E7)^1</f>
@@ -13958,8 +13957,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>151</v>
+      <c r="A20" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="C20" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$9)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$9)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+C7)^1</f>
@@ -13991,8 +13990,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>152</v>
+      <c r="A21" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$9)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$9)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+D7)^1</f>
@@ -14024,8 +14023,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>153</v>
+      <c r="A22" s="11" t="s">
+        <v>152</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$9)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$9)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+E7)^1</f>
@@ -14057,8 +14056,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>154</v>
+      <c r="A23" s="11" t="s">
+        <v>153</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$10)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$10)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+C7)^1</f>
@@ -14090,8 +14089,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>155</v>
+      <c r="A24" s="11" t="s">
+        <v>154</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$10)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$10)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+D7)^1</f>
@@ -14123,8 +14122,8 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>156</v>
+      <c r="A25" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">(((((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$10)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16)-MAX(0,((Operating!$C$10*Operating!$C$11*Operating!$C$12*$B$10)*(1-Operating!$C$14)-Operating!$C$10*Operating!$C$13-Operating!$C$16))*Operating!$C$15)+Operating!$C$16-Operating!$C$17-Operating!$C$18-Operating!$C$19)*Operating!$B$5-Operating!$C$20+IF(1=Operating!$B$7,Operating!$B$6,0))/(1+E7)^1</f>
@@ -14173,7 +14172,7 @@
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -14189,16 +14188,16 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14221,8 +14220,8 @@
       <c r="I2" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>158</v>
+      <c r="A5" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="B5" s="14" t="str">
         <f aca="false">IF(OR(Assumptions!B4="bear",Assumptions!B4="base",Assumptions!B4="bull"),"PASS","FAIL")</f>
@@ -14230,8 +14229,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>159</v>
+      <c r="A6" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="B6" s="14" t="str">
         <f aca="false">IF(Assumptions!$B$10&gt;0,"PASS","FAIL")</f>
@@ -14239,8 +14238,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>160</v>
+      <c r="A7" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="B7" s="14" t="str">
         <f aca="false">IF(ABS(Valuation!B9-(Valuation!B5+Valuation!B6+Valuation!B7-Valuation!B8))&lt;0.01,"PASS","FAIL")</f>
@@ -14248,8 +14247,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>161</v>
+      <c r="A8" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B8" s="14" t="str">
         <f aca="false">IF(ABS(Sensitivities!D9-Valuation!B11)&lt;0.000001,"PASS","FAIL")</f>
@@ -14257,8 +14256,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>162</v>
+      <c r="A9" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B9" s="14" t="str">
         <f aca="false">IF(OR(AND(Assumptions!$B$11="",Assumptions!$B$13=""),AND(ISNUMBER(Assumptions!$B$11),Assumptions!$B$11&gt;0,Assumptions!$B$13&lt;&gt;"")),"PASS","FAIL")</f>
@@ -14266,8 +14265,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>163</v>
+      <c r="A10" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B10" s="14" t="str">
         <f aca="false">IF(AND(Operating!$B$5&gt;=0,Operating!$B$5&lt;=1),"PASS","FAIL")</f>
@@ -14276,7 +14275,7 @@
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -14314,7 +14313,7 @@
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -14330,16 +14329,14 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I85"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="0" width="12.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14363,7 +14360,7 @@
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -14395,7 +14392,7 @@
     </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -14427,7 +14424,7 @@
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -14459,7 +14456,7 @@
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -14491,7 +14488,7 @@
     </row>
     <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -14523,7 +14520,7 @@
     </row>
     <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -14555,7 +14552,7 @@
     </row>
     <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -14587,7 +14584,7 @@
     </row>
     <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -14599,7 +14596,7 @@
     </row>
     <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -14631,7 +14628,7 @@
     </row>
     <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -14663,7 +14660,7 @@
     </row>
     <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -14695,7 +14692,7 @@
     </row>
     <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -14727,7 +14724,7 @@
     </row>
     <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -14759,7 +14756,7 @@
     </row>
     <row r="55" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -14791,7 +14788,7 @@
     </row>
     <row r="59" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -14823,7 +14820,7 @@
     </row>
     <row r="63" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -14855,7 +14852,7 @@
     </row>
     <row r="67" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -14887,7 +14884,7 @@
     </row>
     <row r="71" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -14919,7 +14916,7 @@
     </row>
     <row r="75" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -14951,7 +14948,7 @@
     </row>
     <row r="79" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -14983,7 +14980,7 @@
     </row>
     <row r="83" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -15039,12 +15036,16 @@
     <mergeCell ref="A83:H85"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter>&amp;Lasx-mlx | Readme&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="32" man="true" max="16383" min="0"/>
+    <brk id="66" man="true" max="16383" min="0"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -15055,51 +15056,51 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="22.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.2"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
